--- a/output/full_scan/batch_seq4_2026-10-08.xlsx
+++ b/output/full_scan/batch_seq4_2026-10-08.xlsx
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>67.09388887382138</v>
+        <v>67.09388880251912</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>19.75544127978776</v>
+        <v>19.75544129231452</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.801296590978528</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>76.67342403342252</v>
+        <v>76.67342404566271</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>75.91611015028798</v>
+        <v>75.91611014618826</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>32.20439450645521</v>
+        <v>32.20439452556016</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>4.980673288832757</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4887326327417544</v>
+        <v>0.4887326327862609</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>74.10441611561495</v>
+        <v>74.10441626872807</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>33.18061350349997</v>
+        <v>33.18061367719351</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>4.284743112330164</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1640934753206928</v>
+        <v>0.1640934751871759</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>78.51103423006469</v>
+        <v>78.51103422691453</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>40.04033323739333</v>
+        <v>40.04033318601767</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1.633182894093871</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>2.748429007077867</v>
+        <v>2.748429007378318</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>65.55350813872685</v>
+        <v>65.55350810639274</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>26.49170631051998</v>
+        <v>26.49170631471472</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>3.49917667455105</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-2.977281890585651</v>
+        <v>-2.977281891141942</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>77.46101275402366</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>30.89029563679786</v>
+        <v>30.89029561662684</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>3.251360765817733</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.628319523210112</v>
+        <v>1.628319523221243</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1057.673824849314</v>
+        <v>1057.673824849316</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>182</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>69.82699874310865</v>
+        <v>69.8269987865536</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>17.44512974794898</v>
+        <v>17.44512981539007</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>6.670277194125776</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>2.253903844514367</v>
+        <v>2.253903844180499</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>63.94100546774788</v>
+        <v>63.94100553744212</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>23.00680814396675</v>
+        <v>23.00680821004487</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>0.6067476959557492</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.54508177738284</v>
+        <v>1.545081776047613</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>81.54637256433061</v>
+        <v>81.54637265218614</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>35.09169619230808</v>
+        <v>35.09169625920216</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1.826738239757752</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.5705355314371005</v>
+        <v>0.5705355313480815</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>61.27819713550349</v>
+        <v>61.27819720363324</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>20.27847089854794</v>
+        <v>20.27847085139367</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>1.276432625444525</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.1045743854090559</v>
+        <v>0.1045743855314553</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1012.245727766284</v>
+        <v>1012.245727766283</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>56.1</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>74.91799555783166</v>
+        <v>74.9179954650111</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>38.45204698712477</v>
+        <v>38.45204703677006</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1.713652990355153</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.8169920315177759</v>
+        <v>0.8169920313619925</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>79.68262066623025</v>
+        <v>79.6826206544644</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>33.4742001249915</v>
+        <v>33.47420011595865</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>2.335446992821728</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>5.269218602421052</v>
+        <v>5.26921860233202</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>67.82610279633666</v>
+        <v>67.82610283239651</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>30.96420210068303</v>
+        <v>30.9642021155057</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1.311111908028057</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>48.1591109434649</v>
+        <v>48.15911093678892</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>63.66223206990938</v>
+        <v>63.66223214170211</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>19.39621051957097</v>
+        <v>19.39621048894588</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>8.554352129557817</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.0446004058706429</v>
+        <v>0.0446004058817707</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>74.72584372983073</v>
+        <v>74.72584379359061</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>36.8423470549098</v>
+        <v>36.84234713107922</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>5.266373735378208</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.1095536616446388</v>
+        <v>0.1095536616112545</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>987.7803649217196</v>
+        <v>987.7803649217216</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>30.25</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>64.92127734486857</v>
+        <v>64.92127758012262</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>15.78207423943393</v>
+        <v>15.7820742529968</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>5.725184335850488</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.2029029402986094</v>
+        <v>0.2029029404098802</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>68.77212449507984</v>
+        <v>68.77212450924766</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>30.56750437169348</v>
+        <v>30.56750439392698</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.3826880504152426</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>19.73471335929015</v>
+        <v>19.73471335906756</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>58.28822322619508</v>
+        <v>58.28822323976</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>24.51944124915327</v>
+        <v>24.51944126674284</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.9724842881160614</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.8718063561436917</v>
+        <v>-0.8718063561882063</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>60.19198294960761</v>
+        <v>60.19198296044483</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>48.76985148923677</v>
+        <v>48.76985152550795</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>0.9569706397418086</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.022765632654907</v>
+        <v>-0.0227656326437766</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>72.17429633493799</v>
+        <v>72.17429633842863</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>42.15836750036618</v>
+        <v>42.1583675323041</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>1.588104758620953</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>3.941014259917878</v>
+        <v>3.941014259806643</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>60.7178527316673</v>
+        <v>60.71785273500711</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>14.33134863783929</v>
+        <v>14.33134864042326</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>3.708618875385856</v>
@@ -1651,7 +1651,7 @@
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>923.998448996912</v>
+        <v>923.9984489969104</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>117.5</v>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>64.55973567100359</v>
+        <v>64.55973584720935</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>23.21562930690949</v>
+        <v>23.21562930690948</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1.663024455738727</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.9897603685632848</v>
+        <v>0.9897603678956456</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>69.25451499088646</v>
+        <v>69.25451498373249</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>40.35305418173574</v>
+        <v>40.35305424716466</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>1.078336239530594</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.2730855593219208</v>
+        <v>0.273085559455412</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>90.11777500963332</v>
+        <v>90.1177748058992</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>41.12967411478991</v>
+        <v>41.12967414500749</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>3.899107378906857</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.292520595983463</v>
+        <v>1.292520595961211</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>71.61605728312284</v>
+        <v>71.61605731522687</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>23.89314905777096</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.179208958495864</v>
+        <v>1.17920895847361</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>69.74256626734902</v>
+        <v>69.74256608726876</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>21.69322430430158</v>
+        <v>21.69322430193558</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>3.481635900349015</v>
@@ -1969,7 +1969,7 @@
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>888.6624266132281</v>
+        <v>888.6624266132283</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>744</v>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>70.01756656330483</v>
+        <v>70.01756656947794</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>25.06660472702297</v>
+        <v>25.06660468712722</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>1.042416998156846</v>
@@ -2039,7 +2039,7 @@
         <v>75.19077152037192</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>8.163971100927807</v>
+        <v>8.163971093578551</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>4.302467251014718</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0926419099779521</v>
+        <v>0.0926419099668243</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>58.50761042245218</v>
+        <v>58.50761043031713</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>26.59606417352482</v>
+        <v>26.59606418880803</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>1.206682823039142</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.6845031175793057</v>
+        <v>0.684503117646063</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>67.39992290706094</v>
+        <v>67.39992290549742</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>48.96332836104227</v>
+        <v>48.96332835092778</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.7800935399071472</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>63.33403483506897</v>
+        <v>63.33403483225423</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>20.65802376788539</v>
+        <v>20.65802378431788</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.7298254176322653</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>16.25196644155533</v>
+        <v>16.25196644144413</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>64.37487280742901</v>
+        <v>64.37487282318679</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>28.9951786043114</v>
+        <v>28.99517871633205</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.9363973121766244</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.5156472303551496</v>
+        <v>0.5156472285748137</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>65.5904686776928</v>
+        <v>65.59046874178307</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>19.00221475688292</v>
+        <v>19.0022147701596</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>1.717625777015619</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>32.19725966262747</v>
+        <v>32.19725965928939</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>847.7722747908745</v>
+        <v>847.7722747908743</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>25.1</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>66.86166188321442</v>
+        <v>66.86166202964233</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>31.56371159729808</v>
+        <v>31.56371157195032</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.5378814802682933</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.3381165197351983</v>
+        <v>0.3381165195126572</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>80.80358264827109</v>
+        <v>80.8035826579149</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>19.62477955403521</v>
+        <v>19.62477956343443</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>4.020716508704604</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.661592889688118</v>
+        <v>1.661592889866154</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>55.97856396466149</v>
+        <v>55.97856395107083</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>18.63223916882558</v>
+        <v>18.63223916125901</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>1.672488862215528</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.3963780992707471</v>
+        <v>0.396378099304129</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>77.7020821080412</v>
+        <v>77.70208228059229</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>22.80094266957309</v>
+        <v>22.80094263342174</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>2.539557038644549</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.5305676274250627</v>
+        <v>0.5305676272470286</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>61.59936875471295</v>
+        <v>61.59936876817158</v>
       </c>
       <c r="I40" s="2" t="n">
         <v>20.24097805084357</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.6362717604834478</v>
+        <v>0.6362717604723227</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>73.15394739678554</v>
+        <v>73.15394745535434</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>39.72104326360483</v>
+        <v>39.72104331730154</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>1.445445685811699</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>2.161413221973655</v>
+        <v>2.161413221673214</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>85.3706059208575</v>
+        <v>85.37060587952959</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16.84007431278438</v>
+        <v>16.8400742854249</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>10.11006095586731</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.2258937643450539</v>
+        <v>0.2258937644118184</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>781.0263575891601</v>
+        <v>781.0263575891602</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>22.65</v>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>78.18572053479139</v>
+        <v>78.18572063725328</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>25.59178766913304</v>
+        <v>25.59178760688656</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>11.60849216953814</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.2013236778857524</v>
+        <v>0.2013236777744804</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>66.01950893013475</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>37.11159170493252</v>
+        <v>37.11159181677453</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>1.267323601023024</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.030373884453656</v>
+        <v>-0.0303738845426775</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>54.18396149198882</v>
+        <v>54.18396150038584</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>9.102751658173151</v>
+        <v>9.102751584015804</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>12.31169126946176</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.76963430575598</v>
+        <v>1.769634305589068</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>766.4778215716635</v>
+        <v>766.4778215716636</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>130</v>
@@ -2887,7 +2887,7 @@
         <v>69.21993718134382</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>53.42781488612227</v>
+        <v>53.42781488587472</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>3.147474511367728</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>1.950426053653995</v>
+        <v>1.950426054944753</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>764.6446847593893</v>
+        <v>764.6446847593928</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>28.55</v>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>65.02304809764931</v>
+        <v>65.02304787512651</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>41.89663537867866</v>
+        <v>41.89663554371</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.4094473140236082</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0133844720588593</v>
+        <v>0.0133844724705627</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>62.51530668622535</v>
+        <v>62.51530669922784</v>
       </c>
       <c r="I48" s="2" t="n">
         <v>34.97537735914169</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>3.541107379139589</v>
+        <v>3.541107380029764</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>747.7409278676979</v>
+        <v>747.7409278676981</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>8.26</v>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>76.66691234316079</v>
+        <v>76.66691257698913</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>50.94001713377305</v>
+        <v>50.94001752766246</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.4481584575317622</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1044096426474676</v>
+        <v>0.1044096426169545</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>63.50573106209001</v>
+        <v>63.50573105468303</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>35.12250764894839</v>
+        <v>35.12250758043417</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>2.449054424575288</v>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>70.84441287009956</v>
+        <v>70.84441301782918</v>
       </c>
       <c r="I51" s="2" t="n">
         <v>52.94578964809254</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.0414797152189134</v>
+        <v>-0.0414797151187709</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>727.9536794157679</v>
+        <v>727.9536794157681</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>16.95</v>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>53.88034906346977</v>
+        <v>53.88034904681258</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>10.5582165451718</v>
+        <v>10.55821669762618</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>1.873680353036065</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.1468274278082354</v>
+        <v>0.1468274278527462</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>48.61518805644229</v>
+        <v>48.61518784417077</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>32.40961191904719</v>
+        <v>32.40961212750941</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.8586639754110973</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.9956130900719208</v>
+        <v>0.995613090739552</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>63.94262366936936</v>
+        <v>63.94262374662808</v>
       </c>
       <c r="I54" s="2" t="n">
         <v>15.88210310762525</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>2.948209352842635</v>
+        <v>2.948209352397558</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>54.79146749346229</v>
+        <v>54.7914674900237</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>24.53663914881177</v>
+        <v>24.53663916666669</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>0.969472881262706</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>5.356855591915547</v>
+        <v>5.356855591025251</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>57.23490047440207</v>
+        <v>57.23490046924498</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>30.50586243338505</v>
+        <v>30.50586245902514</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>1.552085417759152</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-17.04353336050971</v>
+        <v>-17.04353335761651</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.41225769082406</v>
+        <v>54.41225754464301</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>37.80303868201877</v>
+        <v>37.80303876057327</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>2.243281616538343</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0056595120897307</v>
+        <v>0.0056595121342383</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>709.1497973563773</v>
+        <v>709.1497973563777</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>243</v>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>60.37772095364354</v>
+        <v>60.37772093703681</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>24.30874443579313</v>
+        <v>24.30874437785427</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.6999553556097393</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>2.373330098668727</v>
+        <v>2.37333009899571</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.97953129629939</v>
+        <v>52.97953130177155</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>21.29962177052312</v>
+        <v>21.29962182074944</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.5548803343323614</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.3257193246607532</v>
+        <v>0.3257193249055519</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>64.91987443746602</v>
+        <v>64.91987442500587</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>21.7630850524037</v>
+        <v>21.76308505328303</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.4822181253006185</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>60.00500448622535</v>
+        <v>60.00500448850147</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>46.61908959273306</v>
+        <v>46.61908941557417</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.4326385735286783</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.7912009807378535</v>
+        <v>0.7912009817059058</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>72.31639243124663</v>
+        <v>72.31639264115084</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>50.56487885756393</v>
+        <v>50.56487913824465</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>1.405236581919744</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.9336613342645408</v>
+        <v>0.9336613335969152</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>54.12648186597372</v>
+        <v>54.12648185601997</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>20.26627635004737</v>
+        <v>20.26627635004738</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>1.128086572407652</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>63.54763158209141</v>
+        <v>63.55678528553226</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>60.7534275000118</v>
+        <v>60.75256155429081</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.9653194621989536</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0528407646873756</v>
+        <v>-0.0528319023226461</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>59.69167335057617</v>
+        <v>59.69167331678901</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>35.81972321790802</v>
+        <v>35.81972325006837</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.6057880814763001</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>3.290945199213162</v>
+        <v>3.290945199992102</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>65.36888482665805</v>
+        <v>65.36888486141302</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>31.69892246878433</v>
+        <v>31.69892249174253</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.5759735147873933</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>1.544016191157662</v>
+        <v>1.544016191280073</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>56.22314110684828</v>
+        <v>56.22314108083786</v>
       </c>
       <c r="I68" s="2" t="n">
         <v>40.38371993468953</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-1.407941822116844</v>
+        <v>-1.407941822228113</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>72.86633041353643</v>
+        <v>72.86633053882404</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>32.0102259285851</v>
+        <v>32.01022598449541</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>0.5993305262015023</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0625920221714817</v>
+        <v>0.06259202210471849</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>57.27288320133541</v>
+        <v>57.27288319963933</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>42.73068078525457</v>
+        <v>42.73068086288401</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.1631578620829101</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-1.526986608633946</v>
+        <v>-1.526986608589454</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>656.6792432276094</v>
+        <v>656.6792432276093</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>102.5</v>
@@ -4209,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>59.30067223990231</v>
+        <v>59.30067230181624</v>
       </c>
       <c r="I71" s="2" t="n">
         <v>48.42255987025601</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.2119028281197872</v>
+        <v>-0.2119028282088075</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>651.9197911813945</v>
+        <v>651.9197911813994</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>139.5</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>69.61211301326441</v>
+        <v>69.61211289635423</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>32.76439732436813</v>
+        <v>32.76439735022078</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.6877564399042813</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>1.30038333944051</v>
+        <v>1.300383339885594</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>643.6799154497959</v>
+        <v>643.6799154498025</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>92.5</v>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>57.86001525246596</v>
+        <v>57.86001530827099</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>27.97747942951612</v>
+        <v>27.97747944584778</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.9319777731144228</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.6461327557725591</v>
+        <v>0.646132755883833</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>57.91815117698569</v>
+        <v>57.9181512578793</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>20.58247843747529</v>
+        <v>20.58247840366455</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.828561700326062</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>1.5547673227779</v>
+        <v>1.554767321442669</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>50.12974649003262</v>
+        <v>50.1297465021113</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>28.06561573901467</v>
+        <v>28.06561582141238</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.6249479924166814</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-22.7173988407275</v>
+        <v>-22.71739885630569</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>57.02039651677057</v>
+        <v>57.02039663771188</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16.19815155431913</v>
+        <v>16.19815157155724</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.5620127583443295</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.1302065168745768</v>
+        <v>0.1302065168968322</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>629.6536270955289</v>
+        <v>629.6536270955629</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>110.5</v>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>60.14601937043511</v>
+        <v>60.14601986453441</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>15.45188789646035</v>
+        <v>15.45188797751494</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>1.083824581378327</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>1.222564894826137</v>
+        <v>1.222564893824704</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>54.64389881225373</v>
+        <v>54.64389884806848</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>20.29394521988112</v>
+        <v>20.29394517326556</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>11.38348338253791</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.5787360537265124</v>
+        <v>0.578736053581867</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>625.624760975933</v>
+        <v>625.6247609759331</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>23.8</v>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>55.41133926642441</v>
+        <v>55.41133930440889</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>27.02130418929162</v>
+        <v>27.021304233913</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.3938106674897973</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0886204311490414</v>
+        <v>0.0886204311379156</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>54.01072970483619</v>
+        <v>54.01072984935174</v>
       </c>
       <c r="I80" s="2" t="n">
         <v>30.53498456372694</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.3089325348384992</v>
+        <v>-0.3089325348718725</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>52.13656380778888</v>
+        <v>52.13656380999916</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>5.298913069780416</v>
+        <v>5.2989130201776</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>2.186653223265486</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.4227276555346848</v>
+        <v>0.422727655501303</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>608.740030436934</v>
+        <v>608.7400304369332</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>68.5</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>55.08529772330152</v>
+        <v>55.08529789487802</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>20.44217128095094</v>
+        <v>20.44217135408256</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>1.29026741443325</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.1659010448876616</v>
+        <v>0.1659010446651208</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>55.8447410227213</v>
+        <v>55.84474104688086</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>22.85736264646</v>
+        <v>22.85736265623897</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>1.043015785714746</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>2.267045370315105</v>
+        <v>2.267045369647486</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>600.1613053541337</v>
+        <v>600.1613053541322</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>137.5</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>62.84268178016745</v>
+        <v>62.84268191839045</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>30.10827841166862</v>
+        <v>30.10827838626104</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>1.011396384596127</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>1.490891737295863</v>
+        <v>1.490891737184588</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>598.4617272982777</v>
+        <v>598.4617272982791</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>46.85</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>57.06517191334064</v>
+        <v>57.06517190268525</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>37.11002749535431</v>
+        <v>37.11002745366471</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.3124976637435426</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0940593806780851</v>
+        <v>0.0940593808561123</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>59.47990641090666</v>
+        <v>59.47990640402943</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>27.83638617223171</v>
+        <v>27.83638624172277</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.62857339212612</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.958274954284882</v>
+        <v>0.9582749543627758</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>581.5200241848354</v>
+        <v>581.5200241848356</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>164.5</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>45.84628472025322</v>
+        <v>45.84628473457605</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>21.26281996569438</v>
+        <v>21.26282007250105</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>0.944798919044052</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-1.519387970026559</v>
+        <v>-1.51938797058291</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>56.99290364652965</v>
+        <v>56.99290358920432</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18.54866615317682</v>
+        <v>18.54866607756906</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>1.245457174478855</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.5092257733198058</v>
+        <v>0.5092257735645969</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>59.5762977537388</v>
+        <v>59.57629766869209</v>
       </c>
       <c r="I89" s="2" t="n">
         <v>18.30082128953971</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.5619132930049779</v>
+        <v>0.5619132929827255</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>63.64965255668138</v>
+        <v>63.64965252516554</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>28.01771512266233</v>
+        <v>28.01771514390524</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>0.5563850025284754</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.2204215943329414</v>
+        <v>0.2204215942661802</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>53.96971348203461</v>
+        <v>53.96971364313105</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>29.78299647479506</v>
+        <v>29.78299658787477</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>0.4039834945725211</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.2567189048134231</v>
+        <v>-0.2567189052918843</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>565.4399524176082</v>
+        <v>565.4399524176081</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>80.59999999999999</v>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>41.98950051748852</v>
+        <v>41.98949989015308</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>23.1488459689246</v>
+        <v>23.14884616586241</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.6635919073195866</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.4741597116325104</v>
+        <v>0.4741597135018773</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>565.3362191069107</v>
+        <v>565.3362191069073</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>736</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>54.44030157766644</v>
+        <v>54.44030157586769</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>15.90192987881019</v>
+        <v>15.90192984687335</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.7081553574532322</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>6.184969877147945</v>
+        <v>6.184969877481749</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>52.4752855932254</v>
+        <v>52.475285541864</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>29.16619446816134</v>
+        <v>29.16619458294041</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.3187633751998095</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0752473549384213</v>
+        <v>0.0752473550185381</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>548.7562256613477</v>
+        <v>548.7562256613479</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>16.4</v>
@@ -5484,7 +5484,7 @@
         <v>56.25998200456838</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>29.04673852879634</v>
+        <v>29.04673853197741</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.4802636838695547</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0828211160705188</v>
+        <v>0.0828211160482643</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>545.4747516685339</v>
+        <v>545.4747516685344</v>
       </c>
       <c r="E96" s="2" t="n">
         <v>106.5</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>47.22372829236041</v>
+        <v>47.22372810038187</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>37.57494580283288</v>
+        <v>37.57494562901514</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.4468643881710906</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.2486579395484343</v>
+        <v>-0.2486579375455462</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>543.4452598472823</v>
+        <v>543.4452598472824</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>24.7</v>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>56.62199254535578</v>
+        <v>56.62199256136655</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>33.62372279271653</v>
+        <v>33.62372278493476</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.3855705628203698</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1435572577959116</v>
+        <v>-0.1435572573063177</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>53.89529960066672</v>
+        <v>53.89529960594769</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>41.28073554978558</v>
+        <v>41.28073566212821</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.5008023932664197</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0319676307812732</v>
+        <v>-0.0319676310705761</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>59.52158623959792</v>
+        <v>59.52158626735923</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>33.74283608677459</v>
+        <v>33.74283612745249</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.4238483017590024</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.5933321865459269</v>
+        <v>0.5933321864791659</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>54.91707968690385</v>
+        <v>54.91707967619488</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>32.60799916250574</v>
+        <v>32.6079992839062</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.4643733875381127</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0185486769148317</v>
+        <v>-0.0185486770038527</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>523.5339755911837</v>
+        <v>523.5339755911845</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>27.75</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>55.82152734964681</v>
+        <v>55.82152737276966</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>35.53424246910125</v>
+        <v>35.53424245910007</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.8985130482593404</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.1974019304996644</v>
+        <v>0.1974019310671507</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>51.35227693084432</v>
+        <v>51.35227676714228</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>21.41194390470204</v>
+        <v>21.41194405622114</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.6135036941499535</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.2811101403546053</v>
+        <v>0.2811101410222112</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>46.17226189861987</v>
+        <v>46.17226192993427</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>21.79183203396551</v>
+        <v>21.79183204089193</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>1.054215616238874</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.4702035780094127</v>
+        <v>0.4702035778313826</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>55.97910482088064</v>
+        <v>55.97910484377472</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>39.3052822428846</v>
+        <v>39.30528223079472</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.161289115239709</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0873621830895564</v>
+        <v>-0.08736218305617589</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>59.5908248658476</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18.51033277749628</v>
+        <v>18.51033277587781</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>0.7912968039168963</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>3.561679418270067</v>
+        <v>3.561679418336824</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>61.53024136654481</v>
+        <v>61.5302413177776</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15.93815205279425</v>
+        <v>15.93815206360343</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.1365662672663774</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0217234757312192</v>
+        <v>-0.0217234757200971</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>514.7189839291847</v>
+        <v>514.7189839291848</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>730</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>52.27339514176997</v>
+        <v>52.27339518570769</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>18.62167224805488</v>
+        <v>18.62167230932579</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.4851692311475426</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.996072604004695</v>
+        <v>0.9960726016679864</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>513.1436866228854</v>
+        <v>513.1436866228855</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>29.35</v>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>44.54642775219882</v>
+        <v>44.54642767767027</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>23.11386166389098</v>
+        <v>23.11386167444858</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.4048494907123954</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0538026453938074</v>
+        <v>0.0538026454383156</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>509.2262466870882</v>
+        <v>509.2262466870883</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>67.5</v>
@@ -6276,7 +6276,7 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>53.28689255752632</v>
+        <v>53.28689251328262</v>
       </c>
       <c r="I110" s="2" t="n">
         <v>30.83001023193654</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.2725479937642192</v>
+        <v>-0.2725479936752073</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>508.9593287917833</v>
+        <v>508.9593287917884</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>29.8</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>56.93423344381312</v>
+        <v>56.93423342591294</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>23.31848837038969</v>
+        <v>23.31848838569075</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>1.376875691648902</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.3175573756596266</v>
+        <v>0.3175573757041353</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>46.82190683116393</v>
+        <v>46.82190683439379</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>24.63838418400112</v>
+        <v>24.63838426831225</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.1530199557362591</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.8088826693712126</v>
+        <v>-0.8088826693823341</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>54.3622667654319</v>
+        <v>54.3622667555762</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>18.30789267047383</v>
+        <v>18.30789270129398</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>1.3923612841366</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.6107583337802529</v>
+        <v>-0.6107583336467055</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>55.81937355590356</v>
+        <v>55.81937343919685</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.3026980050339</v>
+        <v>16.30269801695496</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.5158935174094245</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>50.72034500674981</v>
+        <v>50.72034498624861</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>26.85505367303365</v>
+        <v>26.85505383450873</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.551530874302681</v>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>50.90910836753504</v>
+        <v>50.90910870946581</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>16.63600229742937</v>
+        <v>16.63600229839034</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.449081817245314</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0689976214477046</v>
+        <v>0.06899762149221229</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>497.8203947800248</v>
+        <v>497.8203947800251</v>
       </c>
       <c r="E117" s="2" t="n">
         <v>24.4</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>52.3807638160436</v>
+        <v>52.38076373118806</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>9.082540951258146</v>
+        <v>9.082541014723768</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>1.307367021652736</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0008779775124005</v>
+        <v>-0.0008779774901465</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>58.09532893707398</v>
+        <v>58.09532888407679</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>12.58384668977536</v>
+        <v>12.58384670519779</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>0.7693894625849561</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.1841490338754114</v>
+        <v>0.1841490339087949</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>49.53806308889916</v>
+        <v>49.5380629035802</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>25.42957827007051</v>
+        <v>25.42957852552048</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>0.2309540222741617</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.2805131407892262</v>
+        <v>0.2805131412788234</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>491.1497805726983</v>
+        <v>491.1497805726979</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>24</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>53.56330976098037</v>
+        <v>53.56330995319667</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>18.61698418278615</v>
+        <v>18.61698404371214</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.7046579237562314</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.1683385629038546</v>
+        <v>0.1683385625589084</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>487.8119769855284</v>
+        <v>487.8119769855282</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>2465</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>50.41452760148177</v>
+        <v>50.41452766083094</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>12.04017589698484</v>
+        <v>12.04017598544311</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.6009810078790869</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>12.95456953019219</v>
+        <v>12.95456952574114</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>487.0663308070575</v>
+        <v>487.0663308070574</v>
       </c>
       <c r="E122" s="2" t="n">
         <v>275.5</v>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>49.59392987322097</v>
+        <v>49.59392983525781</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>26.96828816838435</v>
+        <v>26.96828817746997</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>0.8935033295822498</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>1.627597503675316</v>
+        <v>1.627597503341494</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>486.995107911589</v>
+        <v>486.9951079115894</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>667</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>50.60997950955682</v>
+        <v>50.60997944140341</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>17.70625976755545</v>
+        <v>17.7062595666205</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.5842529247834644</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-1.37086376099232</v>
+        <v>-1.370863755539994</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>50.95350093542663</v>
+        <v>50.95350094318252</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>22.93908128892778</v>
+        <v>22.93908118070001</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.2645014108895366</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.180487772344452</v>
+        <v>-0.1804877718659907</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>45.06236027634883</v>
+        <v>45.06236024562617</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>24.87329417909038</v>
+        <v>24.87329421659541</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.6415749955590602</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.6170589768637571</v>
+        <v>-0.6170589768415083</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>474.1183415813757</v>
+        <v>474.1183415813756</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>11.95</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>56.08315883119581</v>
+        <v>56.08315875862958</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>28.74888712278273</v>
+        <v>28.74888714797176</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>0.3115664300400778</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.1211124598742103</v>
+        <v>0.1211124599075922</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>49.10033765274817</v>
+        <v>49.10033774548639</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>29.09754701946076</v>
+        <v>29.09754716330417</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.3024859722355306</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.09603196401863549</v>
+        <v>-0.0960319641187819</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>469.8143395494358</v>
+        <v>469.8143395494471</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>68.3</v>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>50.68913172336541</v>
+        <v>50.68913137304295</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>8.975111764624979</v>
+        <v>8.975111704743016</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>2.84454107596699</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.0436212023386581</v>
+        <v>-0.0436212020716095</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>466.061066826577</v>
+        <v>466.0610668265769</v>
       </c>
       <c r="E129" s="2" t="n">
         <v>14</v>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>52.29296750225582</v>
+        <v>52.292967450224</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>8.936183678245255</v>
+        <v>8.936183727059706</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.3216805805398842</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.0076615867623879</v>
+        <v>0.0076615867735136</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>54.36516164242677</v>
+        <v>54.36516150415726</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>19.91012262975162</v>
+        <v>19.91012262691359</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.2505827141669843</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.1444561888233673</v>
+        <v>0.1444561889123849</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>54.45047937010932</v>
+        <v>54.45047951992812</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>14.9697868231983</v>
+        <v>14.96978691739866</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.5680666130566974</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.930826976051192</v>
+        <v>0.9308269758286588</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.1614144238664314</v>
+        <v>0.1614144239808459</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>54.5460591063196</v>
+        <v>54.54605916972145</v>
       </c>
       <c r="I133" s="2" t="n">
         <v>25.86618503046876</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.1260718952323037</v>
+        <v>0.1260718951432846</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
@@ -7548,10 +7548,10 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>39.52129435173592</v>
+        <v>39.52129437677237</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>17.86941501908542</v>
+        <v>17.86941500301869</v>
       </c>
       <c r="J134" s="2" t="n">
         <v>0.4486713045099861</v>
@@ -7566,7 +7566,7 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-1.660243458096902</v>
+        <v>-1.660243458185919</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>46.65258954236236</v>
+        <v>46.65258947628652</v>
       </c>
       <c r="I135" s="2" t="n">
         <v>23.56211500582556</v>
@@ -7619,7 +7619,7 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>0.1627932243452839</v>
+        <v>0.1627932242228849</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
@@ -7654,10 +7654,10 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>57.75078869693485</v>
+        <v>57.75078881537117</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>14.87302968966516</v>
+        <v>14.87302975108099</v>
       </c>
       <c r="J136" s="2" t="n">
         <v>1.019451029556225</v>
@@ -7672,7 +7672,7 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.3748892361408215</v>
+        <v>0.3748892360851856</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
@@ -7707,10 +7707,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>53.35089448310547</v>
+        <v>53.3508944502703</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>14.39933845670901</v>
+        <v>14.39933839201865</v>
       </c>
       <c r="J137" s="2" t="n">
         <v>0.7289979973697883</v>
@@ -7725,7 +7725,7 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.1127962974303666</v>
+        <v>0.1127962973858579</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>429.6773865088061</v>
+        <v>429.6773865088063</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>50.9</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>49.2633688016675</v>
+        <v>49.26336882827107</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>15.85505776146776</v>
+        <v>15.85505778987623</v>
       </c>
       <c r="J138" s="2" t="n">
         <v>0.3510473491977081</v>
@@ -7778,7 +7778,7 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>0.0345677563407906</v>
+        <v>0.0345677559290864</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>427.9542268949765</v>
+        <v>427.9542268949763</v>
       </c>
       <c r="E139" s="2" t="n">
         <v>99.59999999999999</v>
@@ -7813,10 +7813,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>51.1219327811486</v>
+        <v>51.12193290626543</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>27.06873542372361</v>
+        <v>27.06873536713741</v>
       </c>
       <c r="J139" s="2" t="n">
         <v>0.343976363097106</v>
@@ -7831,7 +7831,7 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>0.3691867748729043</v>
+        <v>0.3691867746503586</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
@@ -7866,10 +7866,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>48.24029460746533</v>
+        <v>48.24029465440055</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>14.7473822347309</v>
+        <v>14.74738223423976</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>0.7819731434266914</v>
@@ -7884,7 +7884,7 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-0.2845898766321926</v>
+        <v>-0.2845898775223843</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>52.61669934594829</v>
+        <v>52.61669931778687</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>12.5261144843529</v>
+        <v>12.52611442928009</v>
       </c>
       <c r="J141" s="2" t="n">
         <v>0.7230220139758849</v>
@@ -7937,7 +7937,7 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.9734472435622026</v>
+        <v>0.9734472492370028</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
@@ -7972,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>46.00579133951696</v>
+        <v>46.0057914011257</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>12.68905803392498</v>
+        <v>12.68905798194766</v>
       </c>
       <c r="J142" s="2" t="n">
         <v>2.64854762471787</v>
@@ -7990,7 +7990,7 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>0.0306828166320874</v>
+        <v>0.0306828166654688</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
@@ -8025,10 +8025,10 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>51.8570354104169</v>
+        <v>51.85703540348837</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>10.78020961350856</v>
+        <v>10.78020962375387</v>
       </c>
       <c r="J143" s="2" t="n">
         <v>0.2204073412871201</v>
@@ -8043,7 +8043,7 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>0.2768396475428115</v>
+        <v>0.2768396475539382</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>419.4527172084557</v>
+        <v>419.4527172084562</v>
       </c>
       <c r="E144" s="2" t="n">
         <v>689</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>49.88788985709071</v>
+        <v>49.88788986490226</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>13.19657344326657</v>
+        <v>13.19657343276548</v>
       </c>
       <c r="J144" s="2" t="n">
         <v>0.7332129705005319</v>
@@ -8096,7 +8096,7 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>5.843202982364506</v>
+        <v>5.843202982698243</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>416.3039440827576</v>
+        <v>416.3039440827574</v>
       </c>
       <c r="E145" s="2" t="n">
         <v>522</v>
@@ -8131,10 +8131,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>47.67685034035782</v>
+        <v>47.67685033471743</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>9.399743396488899</v>
+        <v>9.39974339393803</v>
       </c>
       <c r="J145" s="2" t="n">
         <v>0.5922939554055336</v>
@@ -8149,7 +8149,7 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-0.3091455300869674</v>
+        <v>-0.3091455294193004</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
@@ -8184,10 +8184,10 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>51.99236862157395</v>
+        <v>51.99236863043629</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>26.0534224423298</v>
+        <v>26.05342239343677</v>
       </c>
       <c r="J146" s="2" t="n">
         <v>0.3817014076494666</v>
@@ -8202,7 +8202,7 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>0.1781651352551729</v>
+        <v>0.1781651352774229</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>57.29251992466372</v>
+        <v>57.29251993644752</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>18.10498815876492</v>
+        <v>18.10498816515728</v>
       </c>
       <c r="J147" s="2" t="n">
         <v>1.134572460892089</v>
@@ -8255,7 +8255,7 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>0.4785200921778775</v>
+        <v>0.4785200921333681</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
@@ -8290,10 +8290,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>40.83838597243246</v>
+        <v>40.83838602083936</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>24.33694547661832</v>
+        <v>24.33694545268955</v>
       </c>
       <c r="J148" s="2" t="n">
         <v>0.1320167299257438</v>
@@ -8308,7 +8308,7 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-0.1418635139510018</v>
+        <v>-0.1418635140288918</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v/>
       </c>
       <c r="D149" s="2" t="n">
-        <v>397.4421926891549</v>
+        <v>397.4421926891536</v>
       </c>
       <c r="E149" s="2" t="n">
         <v>51.6</v>
@@ -8343,10 +8343,10 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>52.80259927082779</v>
+        <v>52.80259930497667</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>19.10541746768191</v>
+        <v>19.10541745488217</v>
       </c>
       <c r="J149" s="2" t="n">
         <v>3.643150518598815</v>
@@ -8361,7 +8361,7 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>0.1330273357504176</v>
+        <v>0.1330273357726688</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v/>
       </c>
       <c r="D150" s="2" t="n">
-        <v>394.8525463728923</v>
+        <v>394.8525463728887</v>
       </c>
       <c r="E150" s="2" t="n">
         <v>31.5</v>
@@ -8396,7 +8396,7 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>50.63723860530749</v>
+        <v>50.63723875461148</v>
       </c>
       <c r="I150" s="2" t="n">
         <v>33.25415904748507</v>
@@ -8414,7 +8414,7 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>0.0400141325700799</v>
+        <v>0.0400141328927646</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v/>
       </c>
       <c r="D151" s="2" t="n">
-        <v>393.1790813711893</v>
+        <v>393.179081371189</v>
       </c>
       <c r="E151" s="2" t="n">
         <v>187</v>
@@ -8449,10 +8449,10 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>47.72914843622876</v>
+        <v>47.7291485136235</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>16.3713800018586</v>
+        <v>16.37137995892832</v>
       </c>
       <c r="J151" s="2" t="n">
         <v>1.019350854920576</v>
@@ -8467,7 +8467,7 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>0.9403265363674008</v>
+        <v>0.9403265353659628</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
@@ -8502,10 +8502,10 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>39.3902582438911</v>
+        <v>39.39025839862376</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>20.34374709261317</v>
+        <v>20.34374711683867</v>
       </c>
       <c r="J152" s="2" t="n">
         <v>1.949426029575676</v>
@@ -8520,7 +8520,7 @@
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>-0.0334746260387145</v>
+        <v>-0.0334746259997789</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>52.17865755096937</v>
+        <v>52.17865702378558</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>10.59012960362776</v>
+        <v>10.59012946858293</v>
       </c>
       <c r="J153" s="2" t="n">
         <v>3.032976728796735</v>
@@ -8573,7 +8573,7 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>0.5518135921936432</v>
+        <v>0.5518135994262794</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v/>
       </c>
       <c r="D154" s="2" t="n">
-        <v>386.8914928270821</v>
+        <v>386.891492827081</v>
       </c>
       <c r="E154" s="2" t="n">
         <v>86</v>
@@ -8608,10 +8608,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>53.16201196696361</v>
+        <v>53.16201216934962</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>13.77349180596538</v>
+        <v>13.77349193604485</v>
       </c>
       <c r="J154" s="2" t="n">
         <v>1.209439088401289</v>
@@ -8626,7 +8626,7 @@
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>0.3827656522209307</v>
+        <v>0.3827656512640014</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>51.72730603416446</v>
+        <v>51.72730600902302</v>
       </c>
       <c r="I155" s="2" t="n">
         <v>13.29696028991162</v>
@@ -8679,7 +8679,7 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>0.022622699943362</v>
+        <v>0.0226226998765986</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v/>
       </c>
       <c r="D156" s="2" t="n">
-        <v>374.1373148461546</v>
+        <v>374.1373148461547</v>
       </c>
       <c r="E156" s="2" t="n">
         <v>30.3</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>47.72831139996861</v>
+        <v>47.72831135144389</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>30.87487248473053</v>
+        <v>30.87487239812558</v>
       </c>
       <c r="J156" s="2" t="n">
         <v>0.4531532820330976</v>
@@ -8732,7 +8732,7 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>-0.1664777987321838</v>
+        <v>-0.1664777986431684</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
@@ -8767,10 +8767,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>50.82647095663462</v>
+        <v>50.82647085096925</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>16.88651764384477</v>
+        <v>16.88651768578342</v>
       </c>
       <c r="J157" s="2" t="n">
         <v>0.7301791101965083</v>
@@ -8785,7 +8785,7 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>1.356441004982773</v>
+        <v>1.356441003981336</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
@@ -8820,10 +8820,10 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>42.12408815292608</v>
+        <v>42.12408813069118</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>11.7596150912842</v>
+        <v>11.75961519157851</v>
       </c>
       <c r="J158" s="2" t="n">
         <v>0.6847750350606239</v>
@@ -8838,7 +8838,7 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>-0.03535953369318</v>
+        <v>-0.0353595340825991</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>40.21919960122023</v>
+        <v>40.21919956814661</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>12.35742461513292</v>
+        <v>12.35742463452746</v>
       </c>
       <c r="J159" s="2" t="n">
         <v>0.4099084566107961</v>
@@ -8891,7 +8891,7 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>-0.0286761618844678</v>
+        <v>-0.0286761618177017</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
@@ -8926,10 +8926,10 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>25.51282714747134</v>
+        <v>25.51282741496753</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>30.9121933634217</v>
+        <v>30.91219338168032</v>
       </c>
       <c r="J160" s="2" t="n">
         <v>2.019906786326985</v>
@@ -8944,7 +8944,7 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>-0.0547396682180399</v>
+        <v>-0.0547396679656759</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v/>
       </c>
       <c r="D161" s="2" t="n">
-        <v>363.8032811702528</v>
+        <v>363.8032811702529</v>
       </c>
       <c r="E161" s="2" t="n">
         <v>243</v>
@@ -8982,7 +8982,7 @@
         <v>49.15286327739092</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>8.241265099027343</v>
+        <v>8.241265139100525</v>
       </c>
       <c r="J161" s="2" t="n">
         <v>1.174180378205159</v>
@@ -8997,7 +8997,7 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>1.211389115829913</v>
+        <v>1.211389115162301</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v/>
       </c>
       <c r="D162" s="2" t="n">
-        <v>363.7297658804007</v>
+        <v>363.7297658803997</v>
       </c>
       <c r="E162" s="2" t="n">
         <v>79</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>53.95986460530437</v>
+        <v>53.95986488488517</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>24.40910696217603</v>
+        <v>24.40910693794906</v>
       </c>
       <c r="J162" s="2" t="n">
         <v>1.129148210783265</v>
@@ -9050,7 +9050,7 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>0.2984540420595778</v>
+        <v>0.2984540410581466</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v/>
       </c>
       <c r="D163" s="2" t="n">
-        <v>363.3612866075318</v>
+        <v>363.3612866075299</v>
       </c>
       <c r="E163" s="2" t="n">
         <v>15.5</v>
@@ -9085,10 +9085,10 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>55.61884628258998</v>
+        <v>55.61884627083697</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>28.7712766132632</v>
+        <v>28.77127663820261</v>
       </c>
       <c r="J163" s="2" t="n">
         <v>0.3135702404992454</v>
@@ -9138,10 +9138,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>42.94795063882746</v>
+        <v>42.9479505849769</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>11.83306934391331</v>
+        <v>11.83306929936791</v>
       </c>
       <c r="J164" s="2" t="n">
         <v>0.7064969885120876</v>
@@ -9156,7 +9156,7 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>0.1055857465062441</v>
+        <v>0.1055857465618789</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>48.95853893473031</v>
+        <v>48.95853892888557</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>40.07679398166489</v>
+        <v>40.0767938576472</v>
       </c>
       <c r="J165" s="2" t="n">
         <v>0.8353858063979799</v>
@@ -9209,7 +9209,7 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>-0.0474716557793857</v>
+        <v>-0.0474716557571315</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v/>
       </c>
       <c r="D166" s="2" t="n">
-        <v>355.3648437215064</v>
+        <v>355.3648437215157</v>
       </c>
       <c r="E166" s="2" t="n">
         <v>0</v>
@@ -9244,10 +9244,10 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>35.91364962227732</v>
+        <v>35.91364963665008</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>8.861502038743861</v>
+        <v>8.861501967607136</v>
       </c>
       <c r="J166" s="2" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>-3.112608305489972</v>
+        <v>-3.112608304688815</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v/>
       </c>
       <c r="D167" s="2" t="n">
-        <v>353.7013386826894</v>
+        <v>353.7013386826881</v>
       </c>
       <c r="E167" s="2" t="n">
         <v>26.2</v>
@@ -9297,10 +9297,10 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>61.34420535627584</v>
+        <v>61.34420530978826</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>14.85413403115848</v>
+        <v>14.85413404667984</v>
       </c>
       <c r="J167" s="2" t="n">
         <v>0.3896601480045406</v>
@@ -9315,7 +9315,7 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>0.09616697135795189</v>
+        <v>0.0961669714024608</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v/>
       </c>
       <c r="D168" s="2" t="n">
-        <v>348.3113945597017</v>
+        <v>348.3113945596998</v>
       </c>
       <c r="E168" s="2" t="n">
         <v>20.2</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>44.61820430757509</v>
+        <v>44.61820414675095</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>22.19649743378524</v>
+        <v>22.19649743565588</v>
       </c>
       <c r="J168" s="2" t="n">
         <v>0.294913368565376</v>
@@ -9368,7 +9368,7 @@
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>0.0429595641161944</v>
+        <v>0.0429595640605575</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
@@ -9403,10 +9403,10 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>48.62199315968903</v>
+        <v>48.62199323729158</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>21.51314440881477</v>
+        <v>21.51314438918772</v>
       </c>
       <c r="J169" s="2" t="n">
         <v>0.6122024927061909</v>
@@ -9421,7 +9421,7 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>0.0180958499778774</v>
+        <v>0.0180958499444991</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v/>
       </c>
       <c r="D170" s="2" t="n">
-        <v>348.2602961844262</v>
+        <v>348.2602961844264</v>
       </c>
       <c r="E170" s="2" t="n">
         <v>103.5</v>
@@ -9456,10 +9456,10 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>45.9094449159259</v>
+        <v>45.90944493289205</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>23.58043352332704</v>
+        <v>23.58043356611367</v>
       </c>
       <c r="J170" s="2" t="n">
         <v>0.2627006858368576</v>
@@ -9474,7 +9474,7 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-0.3365779082358049</v>
+        <v>-0.3365779066112591</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>47.74765449924676</v>
+        <v>47.74765463522768</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>29.40065344832317</v>
+        <v>29.40065346786884</v>
       </c>
       <c r="J171" s="2" t="n">
         <v>0.3983863800052102</v>
@@ -9527,7 +9527,7 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>-0.0597898438939903</v>
+        <v>-0.0597898439941349</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v/>
       </c>
       <c r="D172" s="2" t="n">
-        <v>339.8103846020236</v>
+        <v>339.8103846020255</v>
       </c>
       <c r="E172" s="2" t="n">
         <v>19.95</v>
@@ -9562,10 +9562,10 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>54.2282577679168</v>
+        <v>54.22825779315423</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>14.201043688773</v>
+        <v>14.20104376195437</v>
       </c>
       <c r="J172" s="2" t="n">
         <v>0.5459816136949112</v>
@@ -9580,7 +9580,7 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>0.1282175804174053</v>
+        <v>0.1282175804507878</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
@@ -9615,10 +9615,10 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>57.04414421068036</v>
+        <v>57.04414417462872</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>14.33958660582852</v>
+        <v>14.33958666131186</v>
       </c>
       <c r="J173" s="2" t="n">
         <v>0.1512067302569202</v>
@@ -9633,7 +9633,7 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>0.2413814555466059</v>
+        <v>0.2413814555618627</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v/>
       </c>
       <c r="D174" s="2" t="n">
-        <v>326.0050157708854</v>
+        <v>326.0050157708853</v>
       </c>
       <c r="E174" s="2" t="n">
         <v>57.6</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>46.68908225378057</v>
+        <v>46.68908226165423</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>21.83772553597049</v>
+        <v>21.83772555226492</v>
       </c>
       <c r="J174" s="2" t="n">
         <v>0.9412933731729431</v>
@@ -9686,7 +9686,7 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-0.0052537004004641</v>
+        <v>-0.0052537003337025</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v/>
       </c>
       <c r="D175" s="2" t="n">
-        <v>325.9779643327379</v>
+        <v>325.9779643327371</v>
       </c>
       <c r="E175" s="2" t="n">
         <v>73</v>
@@ -9721,10 +9721,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>52.17808185393575</v>
+        <v>52.17808181509183</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>18.87853380141569</v>
+        <v>18.87853384569648</v>
       </c>
       <c r="J175" s="2" t="n">
         <v>0.4617646915224667</v>
@@ -9739,7 +9739,7 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>0.2942439010887555</v>
+        <v>0.2942439014448302</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v/>
       </c>
       <c r="D176" s="2" t="n">
-        <v>322.7041171891268</v>
+        <v>322.7041171891266</v>
       </c>
       <c r="E176" s="2" t="n">
         <v>13.85</v>
@@ -9774,7 +9774,7 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>49.32661806779101</v>
+        <v>49.32661814150362</v>
       </c>
       <c r="I176" s="2" t="n">
         <v>16.56207813939308</v>
@@ -9792,7 +9792,7 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>0.0384753338176904</v>
+        <v>0.0384753338399428</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>40.02220863466523</v>
+        <v>40.02220848262675</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>20.13717710532369</v>
+        <v>20.13717717697218</v>
       </c>
       <c r="J177" s="2" t="n">
         <v>0.744176314688241</v>
@@ -9845,7 +9845,7 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>-0.1360727282498119</v>
+        <v>-0.1360727280717794</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
@@ -9880,10 +9880,10 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>42.78446444129904</v>
+        <v>42.78446442662408</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>24.25781589947788</v>
+        <v>24.25781590816742</v>
       </c>
       <c r="J178" s="2" t="n">
         <v>1.140948457018754</v>
@@ -9898,7 +9898,7 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>0.3926250461727771</v>
+        <v>0.3926250461282701</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
@@ -9933,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>46.73427939904023</v>
+        <v>46.73427976268508</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>26.40537731126366</v>
+        <v>26.4053772979784</v>
       </c>
       <c r="J179" s="2" t="n">
         <v>0.633945087821422</v>
@@ -9951,7 +9951,7 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>-0.0004670771681149</v>
+        <v>-0.0004670772126233</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>35.92952148954905</v>
+        <v>35.92952147607936</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>15.253052774364</v>
+        <v>15.2530527819103</v>
       </c>
       <c r="J180" s="2" t="n">
         <v>1.26677547116854</v>
@@ -10039,10 +10039,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>45.29267442014186</v>
+        <v>45.29267437737455</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>12.70765280372562</v>
+        <v>12.7076528804699</v>
       </c>
       <c r="J181" s="2" t="n">
         <v>0.6131486645636848</v>
@@ -10057,7 +10057,7 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>-0.0838619045747767</v>
+        <v>-0.0838619045413998</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v/>
       </c>
       <c r="D182" s="2" t="n">
-        <v>299.9796664684461</v>
+        <v>299.979666468446</v>
       </c>
       <c r="E182" s="2" t="n">
         <v>169.5</v>
@@ -10092,7 +10092,7 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>36.19265659678197</v>
+        <v>36.19265665109971</v>
       </c>
       <c r="I182" s="2" t="n">
         <v>27.87374409908621</v>
@@ -10110,7 +10110,7 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>-0.5191012790122578</v>
+        <v>-0.5191012799024186</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v/>
       </c>
       <c r="D183" s="2" t="n">
-        <v>291.6444867281484</v>
+        <v>291.6444867281493</v>
       </c>
       <c r="E183" s="2" t="n">
         <v>71.5</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>48.7759053770261</v>
+        <v>48.77590543088824</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>26.73479781624341</v>
+        <v>26.73479777441339</v>
       </c>
       <c r="J183" s="2" t="n">
         <v>0.5203371236699996</v>
@@ -10163,7 +10163,7 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>-0.3699279003199331</v>
+        <v>-0.3699279001418958</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
@@ -10198,10 +10198,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>33.39246908882258</v>
+        <v>33.39246905119093</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>29.48778027426306</v>
+        <v>29.48778028093381</v>
       </c>
       <c r="J184" s="2" t="n">
         <v>1.009739935926595</v>
@@ -10216,7 +10216,7 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>0.3722343468061404</v>
+        <v>0.372234347139952</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
@@ -10251,10 +10251,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>37.62569918798736</v>
+        <v>37.625699246336</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>14.7346245212692</v>
+        <v>14.73462454993427</v>
       </c>
       <c r="J185" s="2" t="n">
         <v>4.117175139191648</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>46.91353438286001</v>
+        <v>46.91353459731035</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>19.80257503529184</v>
+        <v>19.80257500483106</v>
       </c>
       <c r="J186" s="2" t="n">
         <v>1.780959845119442</v>
@@ -10322,7 +10322,7 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>0.223744333318635</v>
+        <v>0.2237443333965316</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
@@ -10357,10 +10357,10 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>42.04158509874387</v>
+        <v>42.04158459086911</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>12.95761953979575</v>
+        <v>12.95761966597489</v>
       </c>
       <c r="J187" s="2" t="n">
         <v>0.5747432519250286</v>
@@ -10375,7 +10375,7 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>0.1465741454231998</v>
+        <v>0.1465741463356198</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
@@ -10410,10 +10410,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>31.0653139376487</v>
+        <v>31.06531393554328</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>14.85746909999227</v>
+        <v>14.85746911581072</v>
       </c>
       <c r="J188" s="2" t="n">
         <v>0.8977382204515161</v>
@@ -10428,7 +10428,7 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>-2.179235520648941</v>
+        <v>-2.179235520760227</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v/>
       </c>
       <c r="D189" s="2" t="n">
-        <v>284.2572298020038</v>
+        <v>284.2572298020035</v>
       </c>
       <c r="E189" s="2" t="n">
         <v>61.6</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>46.91999043786691</v>
+        <v>46.91999047396033</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>19.09140577026153</v>
+        <v>19.0914057830613</v>
       </c>
       <c r="J189" s="2" t="n">
         <v>0.6427299290182241</v>
@@ -10481,7 +10481,7 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>0.1380500220146348</v>
+        <v>0.1380500217030836</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
@@ -10516,10 +10516,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>52.99439768391432</v>
+        <v>52.99439775258264</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>8.534288263205715</v>
+        <v>8.534288276572553</v>
       </c>
       <c r="J190" s="2" t="n">
         <v>0.1265459165530917</v>
@@ -10534,7 +10534,7 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>-0.1244653469738253</v>
+        <v>-0.1244653471296052</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v/>
       </c>
       <c r="D191" s="2" t="n">
-        <v>278.7053137026971</v>
+        <v>278.7053137026973</v>
       </c>
       <c r="E191" s="2" t="n">
         <v>51</v>
@@ -10569,10 +10569,10 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>49.33164391084859</v>
+        <v>49.33164458900558</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>13.66259705574119</v>
+        <v>13.6625971039246</v>
       </c>
       <c r="J191" s="2" t="n">
         <v>1.127451049389059</v>
@@ -10587,7 +10587,7 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>0.2749391233365408</v>
+        <v>0.2749391234478126</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>40.88040611365079</v>
+        <v>40.88040597282907</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>54.07110809666036</v>
+        <v>54.07110817036435</v>
       </c>
       <c r="J192" s="2" t="n">
         <v>0.7959037689469235</v>
@@ -10640,7 +10640,7 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>0.5360718528560144</v>
+        <v>0.5360718530785644</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v/>
       </c>
       <c r="D193" s="2" t="n">
-        <v>270.55278409689</v>
+        <v>270.5527840968899</v>
       </c>
       <c r="E193" s="2" t="n">
         <v>78.3</v>
@@ -10675,10 +10675,10 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>45.5959906505044</v>
+        <v>45.59599057673791</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>18.15807644700023</v>
+        <v>18.15807646810146</v>
       </c>
       <c r="J193" s="2" t="n">
         <v>0.155735852769618</v>
@@ -10693,7 +10693,7 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>-0.4241521388637887</v>
+        <v>-0.4241521380626294</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
@@ -10728,10 +10728,10 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>40.11218970542429</v>
+        <v>40.11218974587291</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>10.17716532928734</v>
+        <v>10.17716552474125</v>
       </c>
       <c r="J194" s="2" t="n">
         <v>0.4198966408268734</v>
@@ -10746,7 +10746,7 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>-0.1314693652102965</v>
+        <v>-0.1314693655441278</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v/>
       </c>
       <c r="D195" s="2" t="n">
-        <v>252.9590810223451</v>
+        <v>252.9590810223449</v>
       </c>
       <c r="E195" s="2" t="n">
         <v>60.6</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>44.27009261179594</v>
+        <v>44.27009257999737</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>13.7593349725635</v>
+        <v>13.75933496994061</v>
       </c>
       <c r="J195" s="2" t="n">
         <v>1.204417450192076</v>
@@ -10799,7 +10799,7 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>-0.2308950320881239</v>
+        <v>-0.2308950319990979</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v/>
       </c>
       <c r="D196" s="2" t="n">
-        <v>251.0053179695241</v>
+        <v>251.0053179695239</v>
       </c>
       <c r="E196" s="2" t="n">
         <v>94.09999999999999</v>
@@ -10834,10 +10834,10 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>39.64944789950747</v>
+        <v>39.64944764294272</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>17.03621772121516</v>
+        <v>17.03621782817924</v>
       </c>
       <c r="J196" s="2" t="n">
         <v>0.8515767503062752</v>
@@ -10852,7 +10852,7 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>-0.220228985896087</v>
+        <v>-0.2202289848946529</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v/>
       </c>
       <c r="D197" s="2" t="n">
-        <v>250.9389602945176</v>
+        <v>250.938960294517</v>
       </c>
       <c r="E197" s="2" t="n">
         <v>10.35</v>
@@ -10887,10 +10887,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>41.36569208695078</v>
+        <v>41.36569206067119</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>29.52090852257491</v>
+        <v>29.5209085164344</v>
       </c>
       <c r="J197" s="2" t="n">
         <v>1.219129832280424</v>
@@ -10905,7 +10905,7 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>-0.0165526690454272</v>
+        <v>-0.0165526690899353</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>48.7459165178397</v>
+        <v>48.74591652697677</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>19.98689572523799</v>
+        <v>19.98689579664809</v>
       </c>
       <c r="J198" s="2" t="n">
         <v>0.7161802872777766</v>
@@ -10958,7 +10958,7 @@
         <v>-1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>0.3671868840363725</v>
+        <v>0.3671868842811703</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v/>
       </c>
       <c r="D199" s="2" t="n">
-        <v>247.1391359099525</v>
+        <v>247.139135909955</v>
       </c>
       <c r="E199" s="2" t="n">
         <v>49.25</v>
@@ -10993,10 +10993,10 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>48.52186799294523</v>
+        <v>48.52186819024806</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>14.87212168351192</v>
+        <v>14.87212176620652</v>
       </c>
       <c r="J199" s="2" t="n">
         <v>0.3976086705563303</v>
@@ -11011,7 +11011,7 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>0.2443609963926651</v>
+        <v>0.2443609962146252</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
@@ -11046,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>45.48990876687873</v>
+        <v>45.48990882815956</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>31.6953690797288</v>
+        <v>31.69536909318328</v>
       </c>
       <c r="J200" s="2" t="n">
         <v>0.5552194094076729</v>
@@ -11064,7 +11064,7 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>-0.0447493549848108</v>
+        <v>-0.0447493550293191</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>36.98924585323281</v>
+        <v>36.98924598389564</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>11.09035297323628</v>
+        <v>11.09035310472384</v>
       </c>
       <c r="J201" s="2" t="n">
         <v>1.018962875164035</v>
@@ -11117,7 +11117,7 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>-0.5173751412749068</v>
+        <v>-0.5173751423653699</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
@@ -11152,10 +11152,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>37.29046830688918</v>
+        <v>37.29046837737806</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>21.25131583288663</v>
+        <v>21.25131590071135</v>
       </c>
       <c r="J202" s="2" t="n">
         <v>0.5531918623868207</v>
@@ -11170,7 +11170,7 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>0.1318088831186963</v>
+        <v>0.1318088831520727</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>54.97755661802348</v>
+        <v>54.97755644870733</v>
       </c>
       <c r="I203" s="2" t="n">
         <v>13.48037425070635</v>
@@ -11223,7 +11223,7 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>0.330815920240864</v>
+        <v>0.330815920129605</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>35.82537369256158</v>
+        <v>35.82537362913216</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>19.74507649581569</v>
+        <v>19.74507650036476</v>
       </c>
       <c r="J204" s="2" t="n">
         <v>0.6015561696571685</v>
@@ -11297,7 +11297,7 @@
         <v/>
       </c>
       <c r="D205" s="2" t="n">
-        <v>227.9705848264965</v>
+        <v>227.9705848264964</v>
       </c>
       <c r="E205" s="2" t="n">
         <v>15.6</v>
@@ -11311,10 +11311,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>47.56906581435585</v>
+        <v>47.56906587667941</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>8.692177982758563</v>
+        <v>8.69217799879539</v>
       </c>
       <c r="J205" s="2" t="n">
         <v>0.8027556281244058</v>
@@ -11329,7 +11329,7 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>0.0570319290319923</v>
+        <v>0.0570319290097373</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v/>
       </c>
       <c r="D206" s="2" t="n">
-        <v>225.6669047448596</v>
+        <v>225.6669047448608</v>
       </c>
       <c r="E206" s="2" t="n">
         <v>73.8</v>
@@ -11364,10 +11364,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>37.32879089166277</v>
+        <v>37.32879062084363</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>12.48255865407315</v>
+        <v>12.48255873721815</v>
       </c>
       <c r="J206" s="2" t="n">
         <v>0.6744532706425037</v>
@@ -11382,7 +11382,7 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>-0.5506287062749048</v>
+        <v>-0.5506287054960065</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v/>
       </c>
       <c r="D207" s="2" t="n">
-        <v>219.41272685525</v>
+        <v>219.4127268552497</v>
       </c>
       <c r="E207" s="2" t="n">
         <v>11.25</v>
@@ -11417,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>43.30475471827037</v>
+        <v>43.3047550283456</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>18.63201963167893</v>
+        <v>18.63201975088905</v>
       </c>
       <c r="J207" s="2" t="n">
         <v>0.5367748653985192</v>
@@ -11435,7 +11435,7 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-0.0390612601960798</v>
+        <v>-0.0390612600736819</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v/>
       </c>
       <c r="D208" s="2" t="n">
-        <v>219.025070110538</v>
+        <v>219.0250701105379</v>
       </c>
       <c r="E208" s="2" t="n">
         <v>17.35</v>
@@ -11470,10 +11470,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>41.86267836424765</v>
+        <v>41.8626782966999</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>16.80718422333897</v>
+        <v>16.80718423965219</v>
       </c>
       <c r="J208" s="2" t="n">
         <v>0.7302326016619191</v>
@@ -11488,7 +11488,7 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>-0.0048713726641705</v>
+        <v>-0.0048713726216638</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v/>
       </c>
       <c r="D209" s="2" t="n">
-        <v>209.7306289869672</v>
+        <v>209.7306289869671</v>
       </c>
       <c r="E209" s="2" t="n">
         <v>18.5</v>
@@ -11523,10 +11523,10 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>25.68225526186993</v>
+        <v>25.68225528315911</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>39.83773769306155</v>
+        <v>39.83773770723344</v>
       </c>
       <c r="J209" s="2" t="n">
         <v>0.295503218764608</v>
@@ -11541,7 +11541,7 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>-0.06648723788489901</v>
+        <v>-0.0664872378960257</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>45.21626093845564</v>
+        <v>45.21626096401687</v>
       </c>
       <c r="I210" s="2" t="n">
         <v>26.99203120614931</v>
@@ -11629,10 +11629,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>42.04979065171687</v>
+        <v>42.04979132443079</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>18.50370373718808</v>
+        <v>18.50370395818301</v>
       </c>
       <c r="J211" s="2" t="n">
         <v>0.8443180061781556</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>-0.07700199074799111</v>
+        <v>-0.0770019915491469</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v/>
       </c>
       <c r="D212" s="2" t="n">
-        <v>179.5476305438224</v>
+        <v>179.5476305438221</v>
       </c>
       <c r="E212" s="2" t="n">
         <v>123.5</v>
@@ -11682,10 +11682,10 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>45.29182895901613</v>
+        <v>45.29182899914638</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>7.502095898114092</v>
+        <v>7.502095955281508</v>
       </c>
       <c r="J212" s="2" t="n">
         <v>0.5033337665933346</v>
@@ -11700,7 +11700,7 @@
         <v>-1</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>0.1731823523101272</v>
+        <v>0.1731823518650477</v>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>35.49117081976</v>
+        <v>35.49117076994925</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>12.06152083125117</v>
+        <v>12.06152083125118</v>
       </c>
       <c r="J213" s="2" t="n">
         <v>1.37491209646732</v>
@@ -11774,7 +11774,7 @@
         <v/>
       </c>
       <c r="D214" s="2" t="n">
-        <v>167.9528976821927</v>
+        <v>167.9528976821928</v>
       </c>
       <c r="E214" s="2" t="n">
         <v>110.5</v>
@@ -11788,10 +11788,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>51.59130263316598</v>
+        <v>51.59130265354641</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>19.47860952377744</v>
+        <v>19.47860951936617</v>
       </c>
       <c r="J214" s="2" t="n">
         <v>0.5884993518823972</v>
@@ -11806,7 +11806,7 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>1.327409057536956</v>
+        <v>1.327409057392304</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
@@ -11841,10 +11841,10 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>44.74057424750612</v>
+        <v>44.74057439358984</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>12.39852806868529</v>
+        <v>12.39852815184873</v>
       </c>
       <c r="J215" s="2" t="n">
         <v>0.3691331351798802</v>
@@ -11859,7 +11859,7 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>-0.0217667191670345</v>
+        <v>-0.0217667191559064</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v/>
       </c>
       <c r="D216" s="2" t="n">
-        <v>155.0800571577176</v>
+        <v>155.0800571577178</v>
       </c>
       <c r="E216" s="2" t="n">
         <v>60.7</v>
@@ -11897,7 +11897,7 @@
         <v>37.40266254749204</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>16.95520119494655</v>
+        <v>16.9552013375014</v>
       </c>
       <c r="J216" s="2" t="n">
         <v>0.6223271994782915</v>
@@ -11912,7 +11912,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>0.1789441308417227</v>
+        <v>0.1789441313758286</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v/>
       </c>
       <c r="D217" s="2" t="n">
-        <v>149.5476668099931</v>
+        <v>149.5476668099933</v>
       </c>
       <c r="E217" s="2" t="n">
         <v>14.5</v>
@@ -11947,10 +11947,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>50.1888505351415</v>
+        <v>50.18885051636709</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>14.88380306357693</v>
+        <v>14.8838030943297</v>
       </c>
       <c r="J217" s="2" t="n">
         <v>0.4040662618474863</v>
@@ -11965,7 +11965,7 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>0.1286082001912149</v>
+        <v>0.1286082002245973</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -12000,10 +12000,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>50.61079842216275</v>
+        <v>50.61079856207949</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>16.9555047070855</v>
+        <v>16.95550470689485</v>
       </c>
       <c r="J218" s="2" t="n">
         <v>0.7032753193057611</v>
@@ -12018,7 +12018,7 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>0.0698231583542023</v>
+        <v>0.0698231583319463</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v/>
       </c>
       <c r="D219" s="2" t="n">
-        <v>143.8008819893757</v>
+        <v>143.8008819893764</v>
       </c>
       <c r="E219" s="2" t="n">
         <v>42.1</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>51.02256770199765</v>
+        <v>51.02256767578415</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>9.39886853158206</v>
+        <v>9.398868562918905</v>
       </c>
       <c r="J219" s="2" t="n">
         <v>0.3806519612675255</v>
@@ -12071,7 +12071,7 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>0.3018795646073636</v>
+        <v>0.3018795647520191</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
@@ -12106,10 +12106,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>48.13639206267119</v>
+        <v>48.13639197231801</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>12.92685616201614</v>
+        <v>12.92685616619942</v>
       </c>
       <c r="J220" s="2" t="n">
         <v>0.2131699292150263</v>
@@ -12124,7 +12124,7 @@
         <v>-1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>-0.0906360840599281</v>
+        <v>-0.0906360841044387</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v/>
       </c>
       <c r="D221" s="2" t="n">
-        <v>116.2751477884265</v>
+        <v>116.275147788426</v>
       </c>
       <c r="E221" s="2" t="n">
         <v>49</v>
@@ -12159,10 +12159,10 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>40.56146969548684</v>
+        <v>40.5614693460153</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>15.32268274483402</v>
+        <v>15.32268281298088</v>
       </c>
       <c r="J221" s="2" t="n">
         <v>1.035506494536956</v>
@@ -12177,7 +12177,7 @@
         <v>-1</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>-0.2257849328787901</v>
+        <v>-0.2257849322334141</v>
       </c>
       <c r="O221" s="2" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v/>
       </c>
       <c r="D222" s="2" t="n">
-        <v>94.85169220505657</v>
+        <v>94.85169220505654</v>
       </c>
       <c r="E222" s="2" t="n">
         <v>37.95</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>41.98483333762987</v>
+        <v>41.98483309885246</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>18.58668840151397</v>
+        <v>18.5866883904592</v>
       </c>
       <c r="J222" s="2" t="n">
         <v>0.6672973893879089</v>
@@ -12230,7 +12230,7 @@
         <v>-1</v>
       </c>
       <c r="N222" s="2" t="n">
-        <v>0.0325814840212969</v>
+        <v>0.0325814839545374</v>
       </c>
       <c r="O222" s="2" t="inlineStr">
         <is>

--- a/output/full_scan/batch_seq4_2026-10-08.xlsx
+++ b/output/full_scan/batch_seq4_2026-10-08.xlsx
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>67.09388880251912</v>
+        <v>67.093888712159</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>19.75544129231452</v>
+        <v>19.75544126539337</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.801296590978528</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>76.67342404566271</v>
+        <v>76.67342402763661</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>75.91611014618826</v>
+        <v>75.91611014913165</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>32.20439452556016</v>
+        <v>32.20439456187114</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>4.980673288832757</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4887326327862609</v>
+        <v>0.48873263279828</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>74.10441626872807</v>
+        <v>74.10441623897773</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>33.18061367719351</v>
+        <v>33.18061371477903</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>4.284743112330164</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1640934751871759</v>
+        <v>0.1640934753073407</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>78.51103422691453</v>
+        <v>78.5110342098636</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>40.04033318601767</v>
+        <v>40.04033315398236</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1.633182894093871</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>2.748429007378318</v>
+        <v>2.748429007510506</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>65.55350810639274</v>
+        <v>65.55350815116304</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>26.49170631471472</v>
+        <v>26.4917063075661</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>3.49917667455105</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-2.977281891141942</v>
+        <v>-2.977281893425264</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>77.46101275402366</v>
+        <v>77.46101275013498</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>30.89029561662684</v>
+        <v>30.89029559492528</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>3.251360765817733</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.628319523221243</v>
+        <v>1.62831952323326</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1057.673824849316</v>
+        <v>1057.673824849314</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>182</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>69.8269987865536</v>
+        <v>69.82699882024879</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>17.44512981539007</v>
+        <v>17.44512984302343</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>6.670277194125776</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>63.94100553744212</v>
+        <v>63.94100548879455</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>23.00680821004487</v>
+        <v>23.00680830208513</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>0.6067476959557492</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.545081776047613</v>
+        <v>1.545081777729973</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>81.54637265218614</v>
+        <v>81.54637263194439</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>35.09169625920216</v>
+        <v>35.09169632138049</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1.826738239757752</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.5705355313480815</v>
+        <v>0.570535531396152</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>61.27819720363324</v>
+        <v>61.27819709881824</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>20.27847085139367</v>
+        <v>20.27847079078144</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>1.276432625444525</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.1045743855314553</v>
+        <v>0.1045743857477651</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>74.9179954650111</v>
+        <v>74.91799563527069</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>38.45204703677006</v>
+        <v>38.45204715209042</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1.713652990355153</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.8169920313619925</v>
+        <v>0.8169920308572651</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>79.6826206544644</v>
+        <v>79.68262065728015</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>33.47420011595865</v>
+        <v>33.47420017347666</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>2.335446992821728</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>5.26921860233202</v>
+        <v>5.269218602019555</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1002.973932479016</v>
+        <v>1002.973932479017</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7165</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>67.82610283239651</v>
+        <v>67.82610281281586</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>30.9642021155057</v>
+        <v>30.96420209303074</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1.311111908028057</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>48.15911093678892</v>
+        <v>48.15911097163905</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>63.66223214170211</v>
+        <v>63.66223210856701</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>19.39621048894588</v>
+        <v>19.39621080582339</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>8.554352129557817</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.0446004058817707</v>
+        <v>0.0446004059779079</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>74.72584379359061</v>
+        <v>74.72584381681467</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>36.84234713107922</v>
@@ -1333,7 +1333,7 @@
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>987.7803649217216</v>
+        <v>987.780364921724</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>30.25</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>64.92127758012262</v>
+        <v>64.92127719297983</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>15.7820742529968</v>
+        <v>15.78207470624739</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>5.725184335850488</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.2029029404098802</v>
+        <v>0.2029029413472302</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>967.5763972541002</v>
+        <v>967.5763972541006</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>1075</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>68.77212450924766</v>
+        <v>68.77212448824727</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>30.56750439392698</v>
+        <v>30.56750435765758</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.3826880504152426</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>19.73471335906756</v>
+        <v>19.73471336135094</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>961.6971495335796</v>
+        <v>961.6971495335794</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>256</v>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>58.28822323976</v>
+        <v>58.28822321483892</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>24.51944126674284</v>
+        <v>24.51944125446673</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.9724842881160614</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.8718063561882063</v>
+        <v>-0.8718063557796274</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>60.19198296044483</v>
+        <v>60.19198296433511</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>48.76985152550795</v>
+        <v>48.7698514967088</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>0.9569706397418086</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.0227656326437766</v>
+        <v>-0.0227656325596572</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>72.17429633842863</v>
+        <v>72.17429633316581</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>42.1583675323041</v>
+        <v>42.15836742306242</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>1.588104758620953</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>60.71785273500711</v>
+        <v>60.71785277816785</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>14.33134864042326</v>
+        <v>14.33134864259433</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>3.708618875385856</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1635115592328782</v>
+        <v>0.1635115592448949</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>923.9984489969104</v>
+        <v>923.9984489969128</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>117.5</v>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>64.55973584720935</v>
+        <v>64.55973565744929</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>23.21562930690948</v>
+        <v>23.21562929241892</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1.663024455738727</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.9897603678956456</v>
+        <v>0.9897603681359758</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>69.25451498373249</v>
+        <v>69.2545149297638</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>40.35305424716466</v>
+        <v>40.35305425904983</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>1.078336239530594</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.273085559455412</v>
+        <v>0.2730855595583881</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>90.1177748058992</v>
+        <v>90.11777503551011</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>41.12967414500749</v>
+        <v>41.12967469801764</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>3.899107378906857</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.292520595961211</v>
+        <v>1.292520595420431</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>71.61605731522687</v>
+        <v>71.61605728500491</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>23.89314905777096</v>
+        <v>23.89314905894293</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>2.035703744266851</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.17920895847361</v>
+        <v>1.179208958653869</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>69.74256608726876</v>
+        <v>69.74256613575191</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>21.69322430193558</v>
+        <v>21.69322425481053</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>3.481635900349015</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.538358370824757</v>
+        <v>1.538358369863364</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>888.6624266132283</v>
+        <v>888.6624266132285</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>744</v>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>70.01756656947794</v>
+        <v>70.01756655041005</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>25.06660468712722</v>
+        <v>25.06660464365764</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>1.042416998156846</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>6.837927481567526</v>
+        <v>6.837927482168492</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>75.19077152037192</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>8.163971093578551</v>
+        <v>8.163971059285624</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>4.302467251014718</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0926419099668243</v>
+        <v>0.09264190995480449</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>58.50761043031713</v>
+        <v>58.50761042749382</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>26.59606418880803</v>
+        <v>26.5960641740593</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>1.206682823039142</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.684503117646063</v>
+        <v>0.6845031177902694</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>67.39992290549742</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>48.96332835092778</v>
+        <v>48.96332836856365</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.7800935399071472</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>18.4771237907529</v>
+        <v>18.47712378955168</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>63.33403483225423</v>
+        <v>63.33403483376986</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>20.65802378431788</v>
+        <v>20.65802378483677</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.7298254176322653</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>16.25196644144413</v>
+        <v>16.25196644084331</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>64.37487282318679</v>
+        <v>64.37487285303519</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>28.99517871633205</v>
+        <v>28.99517869771334</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.9363973121766244</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.5156472285748137</v>
+        <v>0.5156472273731225</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>65.59046874178307</v>
+        <v>65.59046866317249</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>19.0022147701596</v>
+        <v>19.0022147970973</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>1.717625777015619</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>32.19725965928939</v>
+        <v>32.19725966890329</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>847.7722747908743</v>
+        <v>847.7722747908745</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>25.1</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>66.86166202964233</v>
+        <v>66.86166202253159</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>31.56371157195032</v>
+        <v>31.56371141057971</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.5378814802682933</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.3381165195126572</v>
+        <v>0.3381165195607222</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>80.8035826579149</v>
+        <v>80.80358251145896</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>19.62477956343443</v>
+        <v>19.62477952980232</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>4.020716508704604</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.661592889866154</v>
+        <v>1.661592890250709</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>55.97856395107083</v>
+        <v>55.97856396096086</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>18.63223916125901</v>
+        <v>18.6322392701113</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>1.672488862215528</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.396378099304129</v>
+        <v>0.3963780992079853</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>77.70208228059229</v>
+        <v>77.70208214326931</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>22.80094263342174</v>
+        <v>22.80094261552572</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>2.539557038644549</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.5305676272470286</v>
+        <v>0.5305676273792193</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>61.59936876817158</v>
+        <v>61.59936875974893</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>20.24097805084357</v>
+        <v>20.24097800116404</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.9055293371437372</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.6362717604723227</v>
+        <v>0.6362717605564372</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>73.15394745535434</v>
+        <v>73.15394746125094</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>39.72104331730154</v>
+        <v>39.72104334134584</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>1.445445685811699</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>2.161413221673214</v>
+        <v>2.161413221817428</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>85.37060587952959</v>
+        <v>85.37060590899478</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16.8400742854249</v>
+        <v>16.84007425971759</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>10.11006095586731</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.2258937644118184</v>
+        <v>0.2258937643998001</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>78.18572063725328</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>25.59178760688656</v>
+        <v>25.59178763014981</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>11.60849216953814</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.2013236777744804</v>
+        <v>0.2013236777264137</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>66.01950893013475</v>
+        <v>66.01950898592858</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>37.11159181677453</v>
+        <v>37.11159200775838</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>1.267323601023024</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.0303738845426775</v>
+        <v>-0.0303738846388135</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>54.18396150038584</v>
+        <v>54.18396149655202</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>9.102751584015804</v>
+        <v>9.102751596759328</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>12.31169126946176</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.769634305589068</v>
+        <v>1.76963430582942</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>69.21993718134382</v>
+        <v>69.21993712542343</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>53.42781488587472</v>
+        <v>53.42781489307944</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>3.147474511367728</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>1.950426054944753</v>
+        <v>1.950426056338752</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>764.6446847593928</v>
+        <v>764.6446847593895</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>28.55</v>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>65.02304787512651</v>
+        <v>65.02304794912315</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>41.89663554371</v>
+        <v>41.89663556318301</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.4094473140236082</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0133844724705627</v>
+        <v>0.0133844724104768</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>62.51530669922784</v>
+        <v>62.51530668140624</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>34.97537735914169</v>
+        <v>34.9753773510371</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.5042466477427247</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>3.541107380029764</v>
+        <v>3.541107383635008</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>747.7409278676981</v>
+        <v>747.7409278676986</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>8.26</v>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>76.66691257698913</v>
+        <v>76.66691210302247</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>50.94001752766246</v>
+        <v>50.94001900621455</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.4481584575317622</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1044096426169545</v>
+        <v>0.1044096429382452</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>63.50573105468303</v>
+        <v>63.50573102676443</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>35.12250758043417</v>
+        <v>35.12250755181804</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>2.449054424575288</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.498992744281049</v>
+        <v>1.498992744232975</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>70.84441301782918</v>
+        <v>70.84441247502036</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>52.94578964809254</v>
+        <v>52.94578938608861</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>0.3326718561307205</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.0414797151187709</v>
+        <v>-0.0414797145299246</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>727.9536794157681</v>
+        <v>727.9536794157665</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>16.95</v>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>53.88034904681258</v>
+        <v>53.88034905997056</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>10.55821669762618</v>
+        <v>10.55821674737476</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>1.873680353036065</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.1468274278527462</v>
+        <v>0.1468274278166927</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>48.61518784417077</v>
+        <v>48.61518773364862</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>32.40961212750941</v>
+        <v>32.40961208214549</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.8586639754110973</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.995613090739552</v>
+        <v>0.995613090258848</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>63.94262374662808</v>
+        <v>63.94262367389554</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>15.88210310762525</v>
+        <v>15.88210311679728</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>1.288310782535919</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>2.948209352397558</v>
+        <v>2.948209353238754</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>54.7914674900237</v>
+        <v>54.79146746687931</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>24.53663916666669</v>
+        <v>24.53663933942824</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>0.969472881262706</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>5.356855591025251</v>
+        <v>5.356855589102636</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>57.23490046924498</v>
+        <v>57.2349004792418</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>30.50586245902514</v>
+        <v>30.50586244997164</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>1.552085417759152</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-17.04353335761651</v>
+        <v>-17.04353335569381</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.41225754464301</v>
+        <v>54.41225766053554</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>37.80303876057327</v>
+        <v>37.80303880328294</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>2.243281616538343</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0056595121342383</v>
+        <v>0.0056595120981873</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>60.37772093703681</v>
+        <v>60.37772084165312</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>24.30874437785427</v>
+        <v>24.30874436752899</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.6999553556097393</v>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.97953130177155</v>
+        <v>52.979531298825</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>21.29962182074944</v>
+        <v>21.29962176730423</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.5548803343323614</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.3257193249055519</v>
+        <v>0.3257193252180058</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>705.1095629825068</v>
+        <v>705.1095629825046</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>198</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>64.91987442500587</v>
+        <v>64.91987461244592</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>21.76308505328303</v>
+        <v>21.76308509484232</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.4822181253006185</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1.865737402318301</v>
+        <v>1.865737402198118</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>60.00500448850147</v>
+        <v>60.00500449125906</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>46.61908941557417</v>
+        <v>46.61908932166958</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.4326385735286783</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.7912009817059058</v>
+        <v>0.7912009828475455</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>72.31639264115084</v>
+        <v>72.31639264677628</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>50.56487913824465</v>
+        <v>50.56487910464392</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>1.405236581919744</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.9336613335969152</v>
+        <v>0.9336613336449822</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>64.76986699023946</v>
+        <v>64.76986709826687</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>37.48129060517659</v>
+        <v>37.48129062525573</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.8493589426327791</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.2740547604941001</v>
+        <v>0.2740547603619112</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>688.130464261605</v>
+        <v>688.1304642616046</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>188.5</v>
@@ -3841,7 +3841,7 @@
         <v>54.12648185601997</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>20.26627635004738</v>
+        <v>20.26627627967703</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>1.128086572407652</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.07188514784428229</v>
+        <v>0.07188514772411329</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>685.7898084125553</v>
+        <v>685.7898084125552</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>99.40000000000001</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>63.55678528553226</v>
+        <v>63.48449835790602</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>60.75256155429081</v>
+        <v>60.74921335544062</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.9653194621989536</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0528319023226461</v>
+        <v>-0.0528170135764284</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>59.69167331678901</v>
+        <v>59.69167332299459</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>35.81972325006837</v>
+        <v>35.81972335043493</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.6057880814763001</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>3.290945199992102</v>
+        <v>3.290945199150897</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>65.36888486141302</v>
+        <v>65.36888476654997</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>31.69892249174253</v>
+        <v>31.69892262059959</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.5759735147873933</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>1.544016191280073</v>
+        <v>1.544016191808828</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>56.22314108083786</v>
+        <v>56.22314108784067</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>40.38371993468953</v>
+        <v>40.38371975246923</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>0.3704901833757581</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-1.407941822228113</v>
+        <v>-1.407941822540574</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>72.86633053882404</v>
+        <v>72.86633047136149</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>32.01022598449541</v>
+        <v>32.01022602722423</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>0.5993305262015023</v>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>57.27288319963933</v>
+        <v>57.27288320329242</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>42.73068086288401</v>
+        <v>42.7306808853661</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.1631578620829101</v>
@@ -4195,7 +4195,7 @@
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>656.6792432276093</v>
+        <v>656.6792432276094</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>102.5</v>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>59.30067230181624</v>
+        <v>59.30067224491072</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>48.42255987025601</v>
+        <v>48.42255991877536</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.3162313457937626</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.2119028282088075</v>
+        <v>-0.2119028276319721</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>651.9197911813994</v>
+        <v>651.9197911813993</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>139.5</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>69.61211289635423</v>
+        <v>69.61211273718872</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>32.76439735022078</v>
+        <v>32.76439726803947</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.6877564399042813</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>1.300383339885594</v>
+        <v>1.300383339525078</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>643.6799154498025</v>
+        <v>643.6799154497971</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>92.5</v>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>57.86001530827099</v>
+        <v>57.86001539311482</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>27.97747944584778</v>
+        <v>27.97747943386295</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.9319777731144228</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.646132755883833</v>
+        <v>0.6461327564125955</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>57.9181512578793</v>
+        <v>57.91815121432121</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>20.58247840366455</v>
+        <v>20.58247836916069</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.828561700326062</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>1.554767321442669</v>
+        <v>1.554767320721579</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>50.1297465021113</v>
+        <v>50.12974653137886</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>28.06561582141238</v>
+        <v>28.06561583271202</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.6249479924166814</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-22.71739885630569</v>
+        <v>-22.71739886832338</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>57.02039663771188</v>
+        <v>57.02039648150508</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16.19815157155724</v>
+        <v>16.19815195296205</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.5620127583443295</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.1302065168968322</v>
+        <v>0.130206517281382</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>629.6536270955629</v>
+        <v>629.6536270955238</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>110.5</v>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>60.14601986453441</v>
+        <v>60.14601988842445</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>15.45188797751494</v>
+        <v>15.45188795449374</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>1.083824581378327</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>1.222564893824704</v>
+        <v>1.22256489593974</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>54.64389884806848</v>
+        <v>54.64389901105239</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>20.29394517326556</v>
+        <v>20.29394520540497</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>11.38348338253791</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.578736053581867</v>
+        <v>0.5787360535337945</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>55.41133930440889</v>
+        <v>55.4113391494988</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>27.021304233913</v>
+        <v>27.0213042385095</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.3938106674897973</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0886204311379156</v>
+        <v>0.0886204311980015</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>54.01072984935174</v>
+        <v>54.01072967134577</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>30.53498456372694</v>
+        <v>30.53498450024979</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.2982808864335414</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.3089325348718725</v>
+        <v>-0.3089325340306659</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>52.13656380999916</v>
+        <v>52.13656380761887</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>5.2989130201776</v>
+        <v>5.298913014840879</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>2.186653223265486</v>
@@ -4778,7 +4778,7 @@
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>608.7400304369332</v>
+        <v>608.740030436934</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>68.5</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>55.08529789487802</v>
+        <v>55.08529762773695</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>20.44217135408256</v>
+        <v>20.44217150026947</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>1.29026741443325</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.1659010446651208</v>
+        <v>0.1659010450977378</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>55.84474104688086</v>
+        <v>55.84474102086287</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>22.85736265623897</v>
+        <v>22.85736261835515</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>1.043015785714746</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>2.267045369647486</v>
+        <v>2.267045369407138</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>600.1613053541322</v>
+        <v>600.1613053541325</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>137.5</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>62.84268191839045</v>
+        <v>62.84268160704792</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>30.10827838626104</v>
+        <v>30.10827840329526</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>1.011396384596127</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>1.490891737184588</v>
+        <v>1.490891739588054</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>598.4617272982791</v>
+        <v>598.4617272982773</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>46.85</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>57.06517190268525</v>
+        <v>57.06517152495357</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>37.11002745366471</v>
+        <v>37.11002741443554</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.3124976637435426</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0940593808561123</v>
+        <v>0.0940593810243629</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>598.3319117258196</v>
+        <v>598.3319117258192</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>74.40000000000001</v>
@@ -5007,7 +5007,7 @@
         <v>59.47990640402943</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>27.83638624172277</v>
+        <v>27.83638624116447</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.62857339212612</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.9582749543627758</v>
+        <v>0.9582749543747971</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>581.5200241848356</v>
+        <v>581.5200241848355</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>164.5</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>45.84628473457605</v>
+        <v>45.84628501278657</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>21.26282007250105</v>
+        <v>21.26282016072335</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>0.944798919044052</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-1.51938797058291</v>
+        <v>-1.519387970943441</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>56.99290358920432</v>
+        <v>56.99290361306692</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18.54866607756906</v>
+        <v>18.54866607961106</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>1.245457174478855</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.5092257735645969</v>
+        <v>0.5092257734684595</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>59.57629766869209</v>
+        <v>59.57629781056994</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>18.30082128953971</v>
+        <v>18.3008213115125</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.7542019745542025</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.5619132929827255</v>
+        <v>0.5619132927664144</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>63.64965252516554</v>
+        <v>63.64965247991201</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>28.01771514390524</v>
+        <v>28.01771509510158</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>0.5563850025284754</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.2204215942661802</v>
+        <v>0.2204215941580241</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>53.96971364313105</v>
+        <v>53.96971356661537</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>29.78299658787477</v>
+        <v>29.7829966619022</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>0.4039834945725211</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.2567189052918843</v>
+        <v>-0.2567189050154863</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>565.4399524176081</v>
+        <v>565.439952417608</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>80.59999999999999</v>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>41.98949989015308</v>
+        <v>41.98950008195851</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>23.14884616586241</v>
+        <v>23.14884626450048</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.6635919073195866</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.4741597135018773</v>
+        <v>0.4741597130452115</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>565.3362191069073</v>
+        <v>565.3362191069084</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>736</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>54.44030157586769</v>
+        <v>54.44030161848409</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>15.90192984687335</v>
+        <v>15.90192985360913</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.7081553574532322</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>6.184969877481749</v>
+        <v>6.184969877722132</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>52.475285541864</v>
+        <v>52.47528555984991</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>29.16619458294041</v>
+        <v>29.16619455821357</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.3187633751998095</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0752473550185381</v>
+        <v>0.0752473549969067</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>56.25998200456838</v>
+        <v>56.25998201645372</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>29.04673853197741</v>
+        <v>29.04673847476496</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.4802636838695547</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0828211160482643</v>
+        <v>0.0828211160242297</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>545.4747516685344</v>
+        <v>545.4747516685342</v>
       </c>
       <c r="E96" s="2" t="n">
         <v>106.5</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>47.22372810038187</v>
+        <v>47.22372795660228</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>37.57494562901514</v>
+        <v>37.57494552234059</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.4468643881710906</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.2486579375455462</v>
+        <v>-0.2486579368485411</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>543.4452598472824</v>
+        <v>543.4452598472823</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>24.7</v>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>56.62199256136655</v>
+        <v>56.62199254843478</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>33.62372278493476</v>
+        <v>33.62372277766681</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.3855705628203698</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1435572573063177</v>
+        <v>-0.1435572567294865</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>53.89529960594769</v>
+        <v>53.89529995150552</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>41.28073566212821</v>
+        <v>41.28073578439466</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.5008023932664197</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0319676310705761</v>
+        <v>-0.0319676313589918</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>59.52158626735923</v>
+        <v>59.52158634602057</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>33.74283612745249</v>
+        <v>33.74283616548595</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.4238483017590024</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.5933321864791659</v>
+        <v>0.5933321865512684</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>51.27633165307701</v>
+        <v>51.27633164904304</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>5.363244401728139</v>
+        <v>5.363244403664728</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>6.274756516894942</v>
@@ -5802,7 +5802,7 @@
         <v>54.91707967619488</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>32.6079992839062</v>
+        <v>32.60799937109258</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.4643733875381127</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0185486770038527</v>
+        <v>-0.0185486771120049</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>523.5339755911845</v>
+        <v>523.5339755911838</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>27.75</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>55.82152737276966</v>
+        <v>55.82152740265149</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>35.53424245910007</v>
+        <v>35.53424242267603</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.8985130482593404</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.1974019310671507</v>
+        <v>0.1974019317401209</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>51.35227676714228</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>21.41194405622114</v>
+        <v>21.41194406132794</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.6135036941499535</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.2811101410222112</v>
+        <v>0.2811101405415301</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>518.6038912499992</v>
+        <v>518.603891249999</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>46.55</v>
@@ -5961,7 +5961,7 @@
         <v>46.17226192993427</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>21.79183204089193</v>
+        <v>21.79183200010463</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>1.054215616238874</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.4702035778313826</v>
+        <v>0.4702035777112052</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>55.97910484377472</v>
+        <v>55.97910473008467</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>39.30528223079472</v>
+        <v>39.30528213586455</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.161289115239709</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.08736218305617589</v>
+        <v>-0.0873621829720552</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>517.2259988565839</v>
+        <v>517.2259988565841</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>221.5</v>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>59.5908248658476</v>
+        <v>59.59082486239397</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18.51033277587781</v>
+        <v>18.51033268425885</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>0.7912968039168963</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>3.561679418336824</v>
+        <v>3.561679418408914</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>61.5302413177776</v>
+        <v>61.53024137029612</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15.93815206360343</v>
+        <v>15.9381520650347</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.1365662672663774</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0217234757200971</v>
+        <v>-0.0217234757441286</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>514.7189839291848</v>
+        <v>514.7189839291839</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>730</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>52.27339518570769</v>
+        <v>52.27339517170573</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>18.62167230932579</v>
+        <v>18.62167234744785</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.4851692311475426</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.9960726016679864</v>
+        <v>0.9960726022689173</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>44.54642767767027</v>
+        <v>44.54642732305831</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>23.11386167444858</v>
+        <v>23.11386177015942</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.4048494907123954</v>
@@ -6262,7 +6262,7 @@
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>509.2262466870883</v>
+        <v>509.2262466870882</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>67.5</v>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>53.28689251328262</v>
+        <v>53.28689274606108</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>30.83001023193654</v>
+        <v>30.83001024637529</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.1054958924695712</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.2725479936752073</v>
+        <v>-0.2725479938674833</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>508.9593287917884</v>
+        <v>508.9593287917268</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>29.8</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>56.93423342591294</v>
+        <v>56.93423336002242</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>23.31848838569075</v>
+        <v>23.31848827506776</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>1.376875691648902</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.3175573757041353</v>
+        <v>0.3175573757161609</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>46.82190683439379</v>
+        <v>46.821906816258</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>24.63838426831225</v>
+        <v>24.63838421775905</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.1530199557362591</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.8088826693823341</v>
+        <v>-0.8088826693703213</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>54.3622667555762</v>
+        <v>54.36226674288666</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>18.30789270129398</v>
+        <v>18.30789272647134</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>1.3923612841366</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.6107583336467055</v>
+        <v>-0.6107583337668965</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>55.81937343919685</v>
+        <v>55.81937354692613</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.30269801695496</v>
+        <v>16.30269805448696</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.5158935174094245</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.8772126441865241</v>
+        <v>0.8772126433453322</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>502.6464792910931</v>
+        <v>502.6464792910941</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>72</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>50.72034498624861</v>
+        <v>50.72034513703328</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>26.85505383450873</v>
+        <v>26.85505389702237</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.551530874302681</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0735518907551566</v>
+        <v>-0.0735518907791743</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>499.1250281671532</v>
+        <v>499.1250281671531</v>
       </c>
       <c r="E116" s="2" t="n">
         <v>14.2</v>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>50.90910870946581</v>
+        <v>50.90910875967941</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>16.63600229839034</v>
+        <v>16.63600228674744</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.449081817245314</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.06899762149221229</v>
+        <v>0.0689976218046618</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>497.8203947800251</v>
+        <v>497.8203947800248</v>
       </c>
       <c r="E117" s="2" t="n">
         <v>24.4</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>52.38076373118806</v>
+        <v>52.38076376361408</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>9.082541014723768</v>
+        <v>9.082541164710772</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>1.307367021652736</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0008779774901465</v>
+        <v>-0.0008779775021625</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>58.09532888407679</v>
+        <v>58.09532892111415</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>12.58384670519779</v>
+        <v>12.58384674580711</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>0.7693894625849561</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.1841490339087949</v>
+        <v>0.1841490338607269</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>492.6017602671833</v>
+        <v>492.6017602671832</v>
       </c>
       <c r="E119" s="2" t="n">
         <v>43.2</v>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>49.5380629035802</v>
+        <v>49.53806282098099</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>25.42957852552048</v>
+        <v>25.42957849731157</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>0.2309540222741617</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.2805131412788234</v>
+        <v>0.2805131410625173</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>491.1497805726979</v>
+        <v>491.1497805726987</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>24</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>53.56330995319667</v>
+        <v>53.56331018783305</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>18.61698404371214</v>
+        <v>18.616983991701</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.7046579237562314</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.1683385625589084</v>
+        <v>0.1683385624146995</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>487.8119769855282</v>
+        <v>487.811976985528</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>2465</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>50.41452766083094</v>
+        <v>50.41452772930963</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>12.04017598544311</v>
+        <v>12.04017595915746</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.6009810078790869</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>12.95456952574114</v>
+        <v>12.95456953655648</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>487.0663308070574</v>
+        <v>487.0663308070576</v>
       </c>
       <c r="E122" s="2" t="n">
         <v>275.5</v>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>49.59392983525781</v>
+        <v>49.59392987614121</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>26.96828817746997</v>
+        <v>26.96828816969093</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>0.8935033295822498</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>1.627597503341494</v>
+        <v>1.627597502620456</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>486.9951079115894</v>
+        <v>486.9951079115892</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>667</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>50.60997944140341</v>
+        <v>50.6099794245165</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>17.7062595666205</v>
+        <v>17.70625951057859</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.5842529247834644</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-1.370863755539994</v>
+        <v>-1.370863754939164</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>50.95350094318252</v>
+        <v>50.95350084070206</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>22.93908118070001</v>
+        <v>22.93908097416886</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.2645014108895366</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.1804877718659907</v>
+        <v>-0.180487771301175</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>45.06236024562617</v>
+        <v>45.06236022994246</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>24.87329421659541</v>
+        <v>24.87329424037286</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.6415749955590602</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.6170589768415083</v>
+        <v>-0.6170589769136101</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>474.1183415813756</v>
+        <v>474.1183415813753</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>11.95</v>
@@ -7124,7 +7124,7 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>56.08315875862958</v>
+        <v>56.08315887898922</v>
       </c>
       <c r="I126" s="2" t="n">
         <v>28.74888714797176</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.1211124599075922</v>
+        <v>0.1211124598835577</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>49.10033774548639</v>
+        <v>49.10033788153456</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>29.09754716330417</v>
+        <v>29.09754719833127</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.3024859722355306</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0960319641187819</v>
+        <v>-0.0960319640466768</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>469.8143395494471</v>
+        <v>469.8143395494413</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>68.3</v>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>50.68913137304295</v>
+        <v>50.68913150529625</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>8.975111704743016</v>
+        <v>8.975111715759974</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>2.84454107596699</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.0436212020716095</v>
+        <v>-0.0436212024080998</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>466.0610668265769</v>
+        <v>466.061066826577</v>
       </c>
       <c r="E129" s="2" t="n">
         <v>14</v>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>52.292967450224</v>
+        <v>52.29296739162004</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>8.936183727059706</v>
+        <v>8.936183746830404</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.3216805805398842</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.0076615867735136</v>
+        <v>0.0076615867614964</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>54.36516150415726</v>
+        <v>54.36516155974341</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>19.91012262691359</v>
+        <v>19.91012276007887</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.2505827141669843</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.1444561889123849</v>
+        <v>0.1444561888643146</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>54.45047951992812</v>
+        <v>54.45047940781273</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>14.96978691739866</v>
+        <v>14.96978688816628</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.5680666130566974</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.9308269758286588</v>
+        <v>0.9308269772707306</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>59.38159156359779</v>
+        <v>59.38159159779748</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>27.21182808366571</v>
+        <v>27.2118280197165</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>0.576753976717894</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.1614144239808459</v>
+        <v>0.1614144241044313</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>54.54605916972145</v>
+        <v>54.54605921068882</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>25.86618503046876</v>
+        <v>25.86618503162132</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.7342601555104082</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.1260718951432846</v>
+        <v>0.1260718951072341</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
@@ -7548,10 +7548,10 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>39.52129437677237</v>
+        <v>39.52129434367373</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>17.86941500301869</v>
+        <v>17.86941502616379</v>
       </c>
       <c r="J134" s="2" t="n">
         <v>0.4486713045099861</v>
@@ -7566,7 +7566,7 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-1.660243458185919</v>
+        <v>-1.660243458041714</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
@@ -7601,10 +7601,10 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>46.65258947628652</v>
+        <v>46.65258969895266</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>23.56211500582556</v>
+        <v>23.56211494318883</v>
       </c>
       <c r="J135" s="2" t="n">
         <v>16.55888148591724</v>
@@ -7619,7 +7619,7 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>0.1627932242228849</v>
+        <v>0.1627932239705177</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>433.8383129689992</v>
+        <v>433.8383129689993</v>
       </c>
       <c r="E136" s="2" t="n">
         <v>50.7</v>
@@ -7654,10 +7654,10 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>57.75078881537117</v>
+        <v>57.75078863991551</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>14.87302975108099</v>
+        <v>14.87302978226333</v>
       </c>
       <c r="J136" s="2" t="n">
         <v>1.019451029556225</v>
@@ -7672,7 +7672,7 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.3748892360851856</v>
+        <v>0.3748892362654459</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
@@ -7707,10 +7707,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>53.3508944502703</v>
+        <v>53.35089458727219</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>14.39933839201865</v>
+        <v>14.39933840170232</v>
       </c>
       <c r="J137" s="2" t="n">
         <v>0.7289979973697883</v>
@@ -7725,7 +7725,7 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.1127962973858579</v>
+        <v>0.1127962973137538</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>49.26336882827107</v>
+        <v>49.26336881681107</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>15.85505778987623</v>
+        <v>15.85505780691897</v>
       </c>
       <c r="J138" s="2" t="n">
         <v>0.3510473491977081</v>
@@ -7778,7 +7778,7 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>0.0345677559290864</v>
+        <v>0.0345677556046222</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>427.9542268949763</v>
+        <v>427.9542268949767</v>
       </c>
       <c r="E139" s="2" t="n">
         <v>99.59999999999999</v>
@@ -7813,10 +7813,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>51.12193290626543</v>
+        <v>51.12193274355288</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>27.06873536713741</v>
+        <v>27.06873546518465</v>
       </c>
       <c r="J139" s="2" t="n">
         <v>0.343976363097106</v>
@@ -7831,7 +7831,7 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>0.3691867746503586</v>
+        <v>0.3691867758520881</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
@@ -7866,10 +7866,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>48.24029465440055</v>
+        <v>48.24029468472793</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>14.74738223423976</v>
+        <v>14.74738229666844</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>0.7819731434266914</v>
@@ -7884,7 +7884,7 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-0.2845898775223843</v>
+        <v>-0.2845898778828881</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>52.61669931778687</v>
+        <v>52.61669918131236</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>12.52611442928009</v>
+        <v>12.52611436923676</v>
       </c>
       <c r="J141" s="2" t="n">
         <v>0.7230220139758849</v>
@@ -7937,7 +7937,7 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.9734472492370028</v>
+        <v>0.973447254404439</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
@@ -7947,21 +7947,21 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>3672</v>
+        <v>3259</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>康聯訊</t>
+          <t>鑫創</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>425.4854762471787</v>
+        <v>420.5543673224745</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>11.9</v>
+        <v>11.95</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7972,13 +7972,13 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>46.0057914011257</v>
+        <v>51.85703538801113</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>12.68905798194766</v>
+        <v>10.78020964868361</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>2.64854762471787</v>
+        <v>0.2204073412871201</v>
       </c>
       <c r="K142" s="2" t="n">
         <v>0</v>
@@ -7990,31 +7990,31 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>0.0306828166654688</v>
+        <v>0.2768396475419222</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>3259</v>
+        <v>3163</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>鑫創</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>420.5543673224745</v>
+        <v>419.4527172084562</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>11.95</v>
+        <v>689</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -8025,13 +8025,13 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>51.85703540348837</v>
+        <v>49.88788985312483</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>10.78020962375387</v>
+        <v>13.1965734288141</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.2204073412871201</v>
+        <v>0.7332129705005319</v>
       </c>
       <c r="K143" s="2" t="n">
         <v>0</v>
@@ -8043,31 +8043,31 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>0.2768396475539382</v>
+        <v>5.84320298365974</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>3163</v>
+        <v>3450</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>419.4527172084562</v>
+        <v>416.3039440827573</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>689</v>
+        <v>522</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -8078,49 +8078,49 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>49.88788986490226</v>
+        <v>47.6768503194184</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>13.19657343276548</v>
+        <v>9.399743375229418</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.7332129705005319</v>
+        <v>0.5922939554055336</v>
       </c>
       <c r="K144" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L144" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>5.843202982698243</v>
+        <v>-0.3091455290586971</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>3450</v>
+        <v>3481</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>416.3039440827574</v>
+        <v>415.9818290540915</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>522</v>
+        <v>51</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8131,13 +8131,13 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>47.67685033471743</v>
+        <v>51.99236862089223</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>9.39974339393803</v>
+        <v>26.05342236571187</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.5922939554055336</v>
+        <v>0.3817014076494666</v>
       </c>
       <c r="K145" s="2" t="n">
         <v>0</v>
@@ -8149,31 +8149,31 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-0.3091455294193004</v>
+        <v>0.1781651353495259</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>3481</v>
+        <v>3537</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>堡達</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v/>
       </c>
       <c r="D146" s="2" t="n">
-        <v>415.9818290540912</v>
+        <v>413.2214865862797</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>51</v>
+        <v>56.9</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -8184,49 +8184,49 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>51.99236863043629</v>
+        <v>57.29251992375727</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>26.05342239343677</v>
+        <v>18.10498814449031</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.3817014076494666</v>
+        <v>1.134572460892089</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L146" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M146" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>0.1781651352774229</v>
+        <v>0.4785200921333681</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>3537</v>
+        <v>3232</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>堡達</t>
+          <t>昱捷</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>413.2214865862797</v>
+        <v>411.9283316208008</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>56.9</v>
+        <v>19.95</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -8237,16 +8237,16 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>57.29251993644752</v>
+        <v>40.83838594264362</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>18.10498816515728</v>
+        <v>24.33694544845821</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>1.134572460892089</v>
+        <v>0.1320167299257438</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L147" s="2" t="n">
         <v>0</v>
@@ -8255,31 +8255,31 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>0.4785200921333681</v>
+        <v>-0.1418635140649455</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>3232</v>
+        <v>3527</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>昱捷</t>
+          <t>聚積</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v/>
       </c>
       <c r="D148" s="2" t="n">
-        <v>411.9283316208008</v>
+        <v>397.4421926891538</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>19.95</v>
+        <v>51.6</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -8290,16 +8290,16 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>40.83838602083936</v>
+        <v>52.8025991972922</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>24.33694545268955</v>
+        <v>19.1054174642314</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.1320167299257438</v>
+        <v>3.643150518598815</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L148" s="2" t="n">
         <v>0</v>
@@ -8308,31 +8308,31 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-0.1418635140288918</v>
+        <v>0.1330273358928425</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>3527</v>
+        <v>3294</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>聚積</t>
+          <t>英濟</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v/>
       </c>
       <c r="D149" s="2" t="n">
-        <v>397.4421926891536</v>
+        <v>394.8525463728906</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>51.6</v>
+        <v>31.5</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -8343,16 +8343,16 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>52.80259930497667</v>
+        <v>50.63723832338098</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>19.10541745488217</v>
+        <v>33.25415906238629</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>3.643150518598815</v>
+        <v>0.2946538192864885</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L149" s="2" t="n">
         <v>0</v>
@@ -8361,31 +8361,31 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>0.1330273357726688</v>
+        <v>0.0400141335657328</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>3294</v>
+        <v>3227</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>英濟</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v/>
       </c>
       <c r="D150" s="2" t="n">
-        <v>394.8525463728887</v>
+        <v>393.1790813711893</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>31.5</v>
+        <v>187</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -8396,16 +8396,16 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>50.63723875461148</v>
+        <v>47.72914844694495</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>33.25415904748507</v>
+        <v>16.37138000704015</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.2946538192864885</v>
+        <v>1.019350854920576</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L150" s="2" t="n">
         <v>0</v>
@@ -8414,48 +8414,48 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>0.0400141328927646</v>
+        <v>0.9403265348852664</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>3227</v>
+        <v>4155</v>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>訊映</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v/>
       </c>
       <c r="D151" s="2" t="n">
-        <v>393.179081371189</v>
+        <v>390.8966880491806</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>187</v>
+        <v>14.2</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G151" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>47.7291485136235</v>
+        <v>39.39025887472429</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>16.37137995892832</v>
+        <v>20.34374729483955</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>1.019350854920576</v>
+        <v>1.949426029575676</v>
       </c>
       <c r="K151" s="2" t="n">
         <v>0</v>
@@ -8467,48 +8467,48 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>0.9403265353659628</v>
+        <v>-0.0334746258596082</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>4155</v>
+        <v>3629</v>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>訊映</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v/>
       </c>
       <c r="D152" s="2" t="n">
-        <v>390.8966880491808</v>
+        <v>390.8377987508001</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>14.2</v>
+        <v>15.3</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G152" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>39.39025839862376</v>
+        <v>52.17865707429431</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>20.34374711683867</v>
+        <v>10.59012947761442</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>1.949426029575676</v>
+        <v>3.032976728796735</v>
       </c>
       <c r="K152" s="2" t="n">
         <v>0</v>
@@ -8520,31 +8520,31 @@
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>-0.0334746259997789</v>
+        <v>0.5518135990777792</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>3629</v>
+        <v>3528</v>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>地心引力</t>
+          <t>安馳</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
         <v/>
       </c>
       <c r="D153" s="2" t="n">
-        <v>390.8377987508001</v>
+        <v>386.891492827081</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>15.3</v>
+        <v>86</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -8555,16 +8555,16 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>52.17865702378558</v>
+        <v>53.16201204220969</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>10.59012946858293</v>
+        <v>13.77349198088392</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>3.032976728796735</v>
+        <v>1.209439088401289</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L153" s="2" t="n">
         <v>0</v>
@@ -8573,31 +8573,31 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>0.5518135994262794</v>
+        <v>0.3827656510957464</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>3528</v>
+        <v>3716</v>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>安馳</t>
+          <t>中化控股</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
         <v/>
       </c>
       <c r="D154" s="2" t="n">
-        <v>386.891492827081</v>
+        <v>374.2700712391193</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>86</v>
+        <v>34.15</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -8608,13 +8608,13 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>53.16201216934962</v>
+        <v>51.7273061299582</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>13.77349193604485</v>
+        <v>13.29696017177252</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>1.209439088401289</v>
+        <v>0.9667303751267108</v>
       </c>
       <c r="K154" s="2" t="n">
         <v>1</v>
@@ -8626,31 +8626,31 @@
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>0.3827656512640014</v>
+        <v>0.022622699780463</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>3716</v>
+        <v>3380</v>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>中化控股</t>
+          <t>明泰</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v/>
       </c>
       <c r="D155" s="2" t="n">
-        <v>374.2700712391193</v>
+        <v>374.1373148461547</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>34.15</v>
+        <v>30.3</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -8661,49 +8661,49 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>51.72730600902302</v>
+        <v>47.72831133687607</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>13.29696028991162</v>
+        <v>30.87487242958466</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.9667303751267108</v>
+        <v>0.4531532820330976</v>
       </c>
       <c r="K155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L155" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M155" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>0.0226226998765986</v>
+        <v>-0.1664777986672037</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>3380</v>
+        <v>3413</v>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>明泰</t>
+          <t>京鼎</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
         <v/>
       </c>
       <c r="D156" s="2" t="n">
-        <v>374.1373148461547</v>
+        <v>373.0879354522175</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>30.3</v>
+        <v>289.5</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -8714,49 +8714,49 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>47.72831135144389</v>
+        <v>50.82647106717689</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>30.87487239812558</v>
+        <v>16.88651771124536</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.4531532820330976</v>
+        <v>0.7301791101965083</v>
       </c>
       <c r="K156" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L156" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M156" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>-0.1664777986431684</v>
+        <v>1.356441001698075</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>3413</v>
+        <v>3135</v>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>京鼎</t>
+          <t>凌航</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v/>
       </c>
       <c r="D157" s="2" t="n">
-        <v>373.0879354522175</v>
+        <v>370.9673368119302</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>289.5</v>
+        <v>157.5</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -8767,16 +8767,16 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>50.82647085096925</v>
+        <v>42.12408818097625</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>16.88651768578342</v>
+        <v>11.75961521844045</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>0.7301791101965083</v>
+        <v>0.6847750350606239</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L157" s="2" t="n">
         <v>0</v>
@@ -8785,31 +8785,31 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>1.356441003981336</v>
+        <v>-0.0353595347435664</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>3135</v>
+        <v>3704</v>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>凌航</t>
+          <t>合勤控</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v/>
       </c>
       <c r="D158" s="2" t="n">
-        <v>370.9673368119302</v>
+        <v>370.7261174809173</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>157.5</v>
+        <v>39.1</v>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
@@ -8820,16 +8820,16 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>42.12408813069118</v>
+        <v>40.21919954817762</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>11.75961519157851</v>
+        <v>12.35742467944095</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>0.6847750350606239</v>
+        <v>0.4099084566107961</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L158" s="2" t="n">
         <v>0</v>
@@ -8838,7 +8838,7 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>-0.0353595340825991</v>
+        <v>-0.0286761618177017</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
@@ -8848,41 +8848,41 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>3704</v>
+        <v>3625</v>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>合勤控</t>
+          <t>西勝</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v/>
       </c>
       <c r="D159" s="2" t="n">
-        <v>370.7261174809172</v>
+        <v>369.8990431999805</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>39.1</v>
+        <v>10.1</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G159" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>40.21919956814661</v>
+        <v>25.51282748698575</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>12.35742463452746</v>
+        <v>30.91219350001873</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>0.4099084566107961</v>
+        <v>2.019906786326985</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L159" s="2" t="n">
         <v>0</v>
@@ -8891,51 +8891,51 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>-0.0286761618177017</v>
+        <v>-0.0547396674854627</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>3625</v>
+        <v>3672</v>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>西勝</t>
+          <t>康聯訊</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v/>
       </c>
       <c r="D160" s="2" t="n">
-        <v>369.8990431999805</v>
+        <v>365.4854762471787</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>10.1</v>
+        <v>11.9</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G160" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>25.51282741496753</v>
+        <v>46.00579146747357</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>30.91219338168032</v>
+        <v>12.68905800791169</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>2.019906786326985</v>
+        <v>2.64854762471787</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L160" s="2" t="n">
         <v>0</v>
@@ -8944,11 +8944,11 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>-0.0547396679656759</v>
+        <v>0.0306828167736238</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -8965,7 +8965,7 @@
         <v/>
       </c>
       <c r="D161" s="2" t="n">
-        <v>363.8032811702529</v>
+        <v>363.8032811702527</v>
       </c>
       <c r="E161" s="2" t="n">
         <v>243</v>
@@ -8979,10 +8979,10 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>49.15286327739092</v>
+        <v>49.15286332512077</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>8.241265139100525</v>
+        <v>8.241265282044735</v>
       </c>
       <c r="J161" s="2" t="n">
         <v>1.174180378205159</v>
@@ -8997,7 +8997,7 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>1.211389115162301</v>
+        <v>1.21138911444124</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v/>
       </c>
       <c r="D162" s="2" t="n">
-        <v>363.7297658803997</v>
+        <v>363.7297658804005</v>
       </c>
       <c r="E162" s="2" t="n">
         <v>79</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>53.95986488488517</v>
+        <v>53.95986481821479</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>24.40910693794906</v>
+        <v>24.40910700924854</v>
       </c>
       <c r="J162" s="2" t="n">
         <v>1.129148210783265</v>
@@ -9050,7 +9050,7 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>0.2984540410581466</v>
+        <v>0.2984540414186638</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v/>
       </c>
       <c r="D163" s="2" t="n">
-        <v>363.3612866075299</v>
+        <v>363.3612866075318</v>
       </c>
       <c r="E163" s="2" t="n">
         <v>15.5</v>
@@ -9085,10 +9085,10 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>55.61884627083697</v>
+        <v>55.6188462935938</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>28.77127663820261</v>
+        <v>28.7712766457302</v>
       </c>
       <c r="J163" s="2" t="n">
         <v>0.3135702404992454</v>
@@ -9103,7 +9103,7 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>0.0805999281559512</v>
+        <v>0.0805999281439326</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
@@ -9138,10 +9138,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>42.9479505849769</v>
+        <v>42.94795073962465</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>11.83306929936791</v>
+        <v>11.83306930637532</v>
       </c>
       <c r="J164" s="2" t="n">
         <v>0.7064969885120876</v>
@@ -9156,7 +9156,7 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>0.1055857465618789</v>
+        <v>0.1055857465859159</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>48.95853892888557</v>
+        <v>48.95853891051635</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>40.0767938576472</v>
+        <v>40.07679389869715</v>
       </c>
       <c r="J165" s="2" t="n">
         <v>0.8353858063979799</v>
@@ -9209,7 +9209,7 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>-0.0474716557571315</v>
+        <v>-0.0474716557451143</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v/>
       </c>
       <c r="D166" s="2" t="n">
-        <v>355.3648437215157</v>
+        <v>355.3648437215606</v>
       </c>
       <c r="E166" s="2" t="n">
         <v>0</v>
@@ -9244,10 +9244,10 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>35.91364963665008</v>
+        <v>35.91364958939486</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>8.861501967607136</v>
+        <v>8.861501918843855</v>
       </c>
       <c r="J166" s="2" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>-3.112608304688815</v>
+        <v>-3.112608303126565</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v/>
       </c>
       <c r="D167" s="2" t="n">
-        <v>353.7013386826881</v>
+        <v>353.7013386826889</v>
       </c>
       <c r="E167" s="2" t="n">
         <v>26.2</v>
@@ -9297,10 +9297,10 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>61.34420530978826</v>
+        <v>61.34420526661792</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>14.85413404667984</v>
+        <v>14.85413407504633</v>
       </c>
       <c r="J167" s="2" t="n">
         <v>0.3896601480045406</v>
@@ -9315,7 +9315,7 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>0.0961669714024608</v>
+        <v>0.0961669714144778</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v/>
       </c>
       <c r="D168" s="2" t="n">
-        <v>348.3113945596998</v>
+        <v>348.3113945596976</v>
       </c>
       <c r="E168" s="2" t="n">
         <v>20.2</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>44.61820414675095</v>
+        <v>44.6182046070873</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>22.19649743565588</v>
+        <v>22.19649738608117</v>
       </c>
       <c r="J168" s="2" t="n">
         <v>0.294913368565376</v>
@@ -9368,7 +9368,7 @@
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>0.0429595640605575</v>
+        <v>0.0429595638562652</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v/>
       </c>
       <c r="D169" s="2" t="n">
-        <v>348.2848014220861</v>
+        <v>348.284801422086</v>
       </c>
       <c r="E169" s="2" t="n">
         <v>23.9</v>
@@ -9403,10 +9403,10 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>48.62199323729158</v>
+        <v>48.6219931480047</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>21.51314438918772</v>
+        <v>21.51314452247037</v>
       </c>
       <c r="J169" s="2" t="n">
         <v>0.6122024927061909</v>
@@ -9421,7 +9421,7 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>0.0180958499444991</v>
+        <v>0.0180958500766899</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>45.90944493289205</v>
+        <v>45.9094449511633</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>23.58043356611367</v>
+        <v>23.58043362128414</v>
       </c>
       <c r="J170" s="2" t="n">
         <v>0.2627006858368576</v>
@@ -9474,7 +9474,7 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-0.3365779066112591</v>
+        <v>-0.3365779046644566</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>47.74765463522768</v>
+        <v>47.74765452359098</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>29.40065346786884</v>
+        <v>29.40065346215846</v>
       </c>
       <c r="J171" s="2" t="n">
         <v>0.3983863800052102</v>
@@ -9527,7 +9527,7 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>-0.0597898439941349</v>
+        <v>-0.0597898438619445</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v/>
       </c>
       <c r="D172" s="2" t="n">
-        <v>339.8103846020255</v>
+        <v>339.8103846020247</v>
       </c>
       <c r="E172" s="2" t="n">
         <v>19.95</v>
@@ -9562,7 +9562,7 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>54.22825779315423</v>
+        <v>54.22825759926267</v>
       </c>
       <c r="I172" s="2" t="n">
         <v>14.20104376195437</v>
@@ -9580,7 +9580,7 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>0.1282175804507878</v>
+        <v>0.1282175805228907</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
@@ -9615,10 +9615,10 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>57.04414417462872</v>
+        <v>57.04414420526039</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>14.33958666131186</v>
+        <v>14.33958676849953</v>
       </c>
       <c r="J173" s="2" t="n">
         <v>0.1512067302569202</v>
@@ -9633,7 +9633,7 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>0.2413814555618627</v>
+        <v>0.2413814554959561</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>46.68908226165423</v>
+        <v>46.68908219060657</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>21.83772555226492</v>
+        <v>21.83772556373713</v>
       </c>
       <c r="J174" s="2" t="n">
         <v>0.9412933731729431</v>
@@ -9686,7 +9686,7 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-0.0052537003337025</v>
+        <v>-0.0052537002375646</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>52.17808181509183</v>
+        <v>52.17808184437417</v>
       </c>
       <c r="I175" s="2" t="n">
         <v>18.87853384569648</v>
@@ -9739,7 +9739,7 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>0.2942439014448302</v>
+        <v>0.2942439015890311</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
@@ -9774,10 +9774,10 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>49.32661814150362</v>
+        <v>49.32661869718335</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>16.56207813939308</v>
+        <v>16.56207813704636</v>
       </c>
       <c r="J176" s="2" t="n">
         <v>0.365546317292349</v>
@@ -9792,7 +9792,7 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>0.0384753338399428</v>
+        <v>0.0384753339000308</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>40.02220848262675</v>
+        <v>40.02220827980159</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>20.13717717697218</v>
+        <v>20.13717725907966</v>
       </c>
       <c r="J177" s="2" t="n">
         <v>0.744176314688241</v>
@@ -9845,7 +9845,7 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>-0.1360727280717794</v>
+        <v>-0.1360727282880955</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
@@ -9880,10 +9880,10 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>42.78446442662408</v>
+        <v>42.78446446879886</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>24.25781590816742</v>
+        <v>24.25781588775717</v>
       </c>
       <c r="J178" s="2" t="n">
         <v>1.140948457018754</v>
@@ -9898,7 +9898,7 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>0.3926250461282701</v>
+        <v>0.3926250460321319</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v/>
       </c>
       <c r="D179" s="2" t="n">
-        <v>319.7726019234998</v>
+        <v>319.7726019234999</v>
       </c>
       <c r="E179" s="2" t="n">
         <v>7.09</v>
@@ -9933,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>46.73427976268508</v>
+        <v>46.73427937106756</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>26.4053772979784</v>
+        <v>26.40537732923016</v>
       </c>
       <c r="J179" s="2" t="n">
         <v>0.633945087821422</v>
@@ -9972,7 +9972,7 @@
         <v/>
       </c>
       <c r="D180" s="2" t="n">
-        <v>312.9446116233181</v>
+        <v>312.9446116233196</v>
       </c>
       <c r="E180" s="2" t="n">
         <v>158</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>35.92952147607936</v>
+        <v>35.92952157680904</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>15.2530527819103</v>
+        <v>15.25305270072439</v>
       </c>
       <c r="J180" s="2" t="n">
         <v>1.26677547116854</v>
@@ -10004,7 +10004,7 @@
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>-1.797779330329669</v>
+        <v>-1.797779330618086</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v/>
       </c>
       <c r="D181" s="2" t="n">
-        <v>304.5268200296261</v>
+        <v>304.5268200296259</v>
       </c>
       <c r="E181" s="2" t="n">
         <v>34.2</v>
@@ -10039,10 +10039,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>45.29267437737455</v>
+        <v>45.29267450765517</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>12.7076528804699</v>
+        <v>12.70765289092929</v>
       </c>
       <c r="J181" s="2" t="n">
         <v>0.6131486645636848</v>
@@ -10057,7 +10057,7 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>-0.0838619045413998</v>
+        <v>-0.0838619045534128</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
@@ -10092,10 +10092,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>36.19265665109971</v>
+        <v>36.19265657797968</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>27.87374409908621</v>
+        <v>27.87374412568824</v>
       </c>
       <c r="J182" s="2" t="n">
         <v>0.5018784902384519</v>
@@ -10131,7 +10131,7 @@
         <v/>
       </c>
       <c r="D183" s="2" t="n">
-        <v>291.6444867281493</v>
+        <v>291.6444867281504</v>
       </c>
       <c r="E183" s="2" t="n">
         <v>71.5</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>48.77590543088824</v>
+        <v>48.77590527280348</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>26.73479777441339</v>
+        <v>26.73479780739272</v>
       </c>
       <c r="J183" s="2" t="n">
         <v>0.5203371236699996</v>
@@ -10163,7 +10163,7 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>-0.3699279001418958</v>
+        <v>-0.369927899745319</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
@@ -10198,10 +10198,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>33.39246905119093</v>
+        <v>33.39246862474636</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>29.48778028093381</v>
+        <v>29.48778024242065</v>
       </c>
       <c r="J184" s="2" t="n">
         <v>1.009739935926595</v>
@@ -10216,7 +10216,7 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>0.372234347139952</v>
+        <v>0.3722343473802958</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
@@ -10251,10 +10251,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>37.625699246336</v>
+        <v>37.62569898134007</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>14.73462454993427</v>
+        <v>14.73462454547965</v>
       </c>
       <c r="J185" s="2" t="n">
         <v>4.117175139191648</v>
@@ -10269,7 +10269,7 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>-0.004820712679872</v>
+        <v>-0.0048207126438191</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>46.91353459731035</v>
+        <v>46.91353427944789</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>19.80257500483106</v>
+        <v>19.8025747839276</v>
       </c>
       <c r="J186" s="2" t="n">
         <v>1.780959845119442</v>
@@ -10322,7 +10322,7 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>0.2237443333965316</v>
+        <v>0.2237443344660693</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
@@ -10357,10 +10357,10 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>42.04158459086911</v>
+        <v>42.0415846976562</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>12.95761966597489</v>
+        <v>12.95761980519566</v>
       </c>
       <c r="J187" s="2" t="n">
         <v>0.5747432519250286</v>
@@ -10375,7 +10375,7 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>0.1465741463356198</v>
+        <v>0.1465741460472114</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v/>
       </c>
       <c r="D188" s="2" t="n">
-        <v>284.407181288869</v>
+        <v>284.4071812888455</v>
       </c>
       <c r="E188" s="2" t="n">
         <v>362.5</v>
@@ -10410,10 +10410,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>31.06531393554328</v>
+        <v>31.06531392571802</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>14.85746911581072</v>
+        <v>14.85746917775252</v>
       </c>
       <c r="J188" s="2" t="n">
         <v>0.8977382204515161</v>
@@ -10428,7 +10428,7 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>-2.179235520760227</v>
+        <v>-2.179235520952509</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v/>
       </c>
       <c r="D189" s="2" t="n">
-        <v>284.2572298020035</v>
+        <v>284.2572298020029</v>
       </c>
       <c r="E189" s="2" t="n">
         <v>61.6</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>46.91999047396033</v>
+        <v>46.91999053059583</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>19.0914057830613</v>
+        <v>19.09140580273507</v>
       </c>
       <c r="J189" s="2" t="n">
         <v>0.6427299290182241</v>
@@ -10481,7 +10481,7 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>0.1380500217030836</v>
+        <v>0.138050021558867</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v/>
       </c>
       <c r="D190" s="2" t="n">
-        <v>280.2753171438002</v>
+        <v>280.2753171438001</v>
       </c>
       <c r="E190" s="2" t="n">
         <v>8.199999999999999</v>
@@ -10516,10 +10516,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>52.99439775258264</v>
+        <v>52.99439767863213</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>8.534288276572553</v>
+        <v>8.534288376650135</v>
       </c>
       <c r="J190" s="2" t="n">
         <v>0.1265459165530917</v>
@@ -10534,7 +10534,7 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>-0.1244653471296052</v>
+        <v>-0.1244653471776741</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
@@ -10569,10 +10569,10 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>49.33164458900558</v>
+        <v>49.3316445444737</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>13.6625971039246</v>
+        <v>13.66259736480756</v>
       </c>
       <c r="J191" s="2" t="n">
         <v>1.127451049389059</v>
@@ -10587,7 +10587,7 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>0.2749391234478126</v>
+        <v>0.2749391255388276</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>40.88040597282907</v>
+        <v>40.88040594183065</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>54.07110817036435</v>
+        <v>54.071108228233</v>
       </c>
       <c r="J192" s="2" t="n">
         <v>0.7959037689469235</v>
@@ -10640,7 +10640,7 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>0.5360718530785644</v>
+        <v>0.5360718528382091</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v/>
       </c>
       <c r="D193" s="2" t="n">
-        <v>270.5527840968899</v>
+        <v>270.5527840968897</v>
       </c>
       <c r="E193" s="2" t="n">
         <v>78.3</v>
@@ -10675,10 +10675,10 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>45.59599057673791</v>
+        <v>45.59599050612383</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>18.15807646810146</v>
+        <v>18.15807644728948</v>
       </c>
       <c r="J193" s="2" t="n">
         <v>0.155735852769618</v>
@@ -10693,7 +10693,7 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>-0.4241521380626294</v>
+        <v>-0.4241521376300129</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>40.11218974587291</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>10.17716552474125</v>
+        <v>10.17716564647412</v>
       </c>
       <c r="J194" s="2" t="n">
         <v>0.4198966408268734</v>
@@ -10746,7 +10746,7 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>-0.1314693655441278</v>
+        <v>-0.1314693657844572</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v/>
       </c>
       <c r="D195" s="2" t="n">
-        <v>252.9590810223449</v>
+        <v>252.9590810223451</v>
       </c>
       <c r="E195" s="2" t="n">
         <v>60.6</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>44.27009257999737</v>
+        <v>44.27009255956084</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>13.75933496994061</v>
+        <v>13.75933488396392</v>
       </c>
       <c r="J195" s="2" t="n">
         <v>1.204417450192076</v>
@@ -10799,7 +10799,7 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>-0.2308950319990979</v>
+        <v>-0.2308950319870871</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v/>
       </c>
       <c r="D196" s="2" t="n">
-        <v>251.0053179695239</v>
+        <v>251.0053179695237</v>
       </c>
       <c r="E196" s="2" t="n">
         <v>94.09999999999999</v>
@@ -10834,10 +10834,10 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>39.64944764294272</v>
+        <v>39.64944786887378</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>17.03621782817924</v>
+        <v>17.03621789708124</v>
       </c>
       <c r="J196" s="2" t="n">
         <v>0.8515767503062752</v>
@@ -10852,7 +10852,7 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>-0.2202289848946529</v>
+        <v>-0.2202289852551693</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v/>
       </c>
       <c r="D197" s="2" t="n">
-        <v>250.938960294517</v>
+        <v>250.9389602945169</v>
       </c>
       <c r="E197" s="2" t="n">
         <v>10.35</v>
@@ -10887,10 +10887,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>41.36569206067119</v>
+        <v>41.36569217387557</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>29.5209085164344</v>
+        <v>29.52090864345766</v>
       </c>
       <c r="J197" s="2" t="n">
         <v>1.219129832280424</v>
@@ -10905,7 +10905,7 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>-0.0165526690899353</v>
+        <v>-0.0165526691500202</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>48.74591652697677</v>
+        <v>48.74591645809734</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>19.98689579664809</v>
+        <v>19.98689582103434</v>
       </c>
       <c r="J198" s="2" t="n">
         <v>0.7161802872777766</v>
@@ -10958,7 +10958,7 @@
         <v>-1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>0.3671868842811703</v>
+        <v>0.3671868845695808</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v/>
       </c>
       <c r="D199" s="2" t="n">
-        <v>247.139135909955</v>
+        <v>247.1391359099541</v>
       </c>
       <c r="E199" s="2" t="n">
         <v>49.25</v>
@@ -10993,10 +10993,10 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>48.52186819024806</v>
+        <v>48.52186792933501</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>14.87212176620652</v>
+        <v>14.87212182598371</v>
       </c>
       <c r="J199" s="2" t="n">
         <v>0.3976086705563303</v>
@@ -11011,7 +11011,7 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>0.2443609962146252</v>
+        <v>0.2443609964309344</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v/>
       </c>
       <c r="D200" s="2" t="n">
-        <v>243.3152281416457</v>
+        <v>243.3152281416459</v>
       </c>
       <c r="E200" s="2" t="n">
         <v>13.15</v>
@@ -11046,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>45.48990882815956</v>
+        <v>45.48990878755577</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>31.69536909318328</v>
+        <v>31.69536904662113</v>
       </c>
       <c r="J200" s="2" t="n">
         <v>0.5552194094076729</v>
@@ -11064,7 +11064,7 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>-0.0447493550293191</v>
+        <v>-0.0447493550173034</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>36.98924598389564</v>
+        <v>36.98924597486869</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>11.09035310472384</v>
+        <v>11.09035311461041</v>
       </c>
       <c r="J201" s="2" t="n">
         <v>1.018962875164035</v>
@@ -11117,7 +11117,7 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>-0.5173751423653699</v>
+        <v>-0.5173751419327528</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
@@ -11152,10 +11152,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>37.29046837737806</v>
+        <v>37.2904682173441</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>21.25131590071135</v>
+        <v>21.25131594799402</v>
       </c>
       <c r="J202" s="2" t="n">
         <v>0.5531918623868207</v>
@@ -11170,7 +11170,7 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>0.1318088831520727</v>
+        <v>0.1318088832722505</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
@@ -11205,10 +11205,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>54.97755644870733</v>
+        <v>54.9775567512944</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>13.48037425070635</v>
+        <v>13.48037420898009</v>
       </c>
       <c r="J203" s="2" t="n">
         <v>1.253572668288867</v>
@@ -11223,7 +11223,7 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>0.330815920129605</v>
+        <v>0.3308159195287478</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>35.82537362913216</v>
+        <v>35.82537345836062</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>19.74507650036476</v>
+        <v>19.74507644817224</v>
       </c>
       <c r="J204" s="2" t="n">
         <v>0.6015561696571685</v>
@@ -11276,7 +11276,7 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>-0.0041293283771242</v>
+        <v>-0.0041293284011568</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
@@ -11311,10 +11311,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>47.56906587667941</v>
+        <v>47.56906582220965</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>8.69217799879539</v>
+        <v>8.692178058946157</v>
       </c>
       <c r="J205" s="2" t="n">
         <v>0.8027556281244058</v>
@@ -11329,7 +11329,7 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>0.0570319290097373</v>
+        <v>0.0570319290457906</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v/>
       </c>
       <c r="D206" s="2" t="n">
-        <v>225.6669047448608</v>
+        <v>225.6669047448605</v>
       </c>
       <c r="E206" s="2" t="n">
         <v>73.8</v>
@@ -11364,10 +11364,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>37.32879062084363</v>
+        <v>37.32879065787336</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>12.48255873721815</v>
+        <v>12.48255874199685</v>
       </c>
       <c r="J206" s="2" t="n">
         <v>0.6744532706425037</v>
@@ -11382,7 +11382,7 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>-0.5506287054960065</v>
+        <v>-0.5506287059766919</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v/>
       </c>
       <c r="D207" s="2" t="n">
-        <v>219.4127268552497</v>
+        <v>219.412726855249</v>
       </c>
       <c r="E207" s="2" t="n">
         <v>11.25</v>
@@ -11417,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>43.3047550283456</v>
+        <v>43.30475440107877</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>18.63201975088905</v>
+        <v>18.63202041202289</v>
       </c>
       <c r="J207" s="2" t="n">
         <v>0.5367748653985192</v>
@@ -11435,7 +11435,7 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-0.0390612600736819</v>
+        <v>-0.0390612597492143</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v/>
       </c>
       <c r="D208" s="2" t="n">
-        <v>219.0250701105379</v>
+        <v>219.0250701105381</v>
       </c>
       <c r="E208" s="2" t="n">
         <v>17.35</v>
@@ -11470,10 +11470,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>41.8626782966999</v>
+        <v>41.86267833343305</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>16.80718423965219</v>
+        <v>16.80718413099457</v>
       </c>
       <c r="J208" s="2" t="n">
         <v>0.7302326016619191</v>
@@ -11488,7 +11488,7 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>-0.0048713726216638</v>
+        <v>-0.0048713726569775</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v/>
       </c>
       <c r="D209" s="2" t="n">
-        <v>209.7306289869671</v>
+        <v>209.7306289869672</v>
       </c>
       <c r="E209" s="2" t="n">
         <v>18.5</v>
@@ -11523,10 +11523,10 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>25.68225528315911</v>
+        <v>25.68225525434418</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>39.83773770723344</v>
+        <v>39.83773771061976</v>
       </c>
       <c r="J209" s="2" t="n">
         <v>0.295503218764608</v>
@@ -11541,7 +11541,7 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>-0.0664872378960257</v>
+        <v>-0.06648723788400659</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>45.21626096401687</v>
+        <v>45.21626137692902</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>26.99203120614931</v>
+        <v>26.99203124942097</v>
       </c>
       <c r="J210" s="2" t="n">
         <v>0.4011067590764831</v>
@@ -11594,7 +11594,7 @@
         <v>-1</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>0.0047728386668821</v>
+        <v>0.0047728386789002</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
@@ -11629,10 +11629,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>42.04979132443079</v>
+        <v>42.04979115002347</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>18.50370395818301</v>
+        <v>18.50370395553941</v>
       </c>
       <c r="J211" s="2" t="n">
         <v>0.8443180061781556</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>-0.0770019915491469</v>
+        <v>-0.0770019917654592</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v/>
       </c>
       <c r="D212" s="2" t="n">
-        <v>179.5476305438221</v>
+        <v>179.5476305438229</v>
       </c>
       <c r="E212" s="2" t="n">
         <v>123.5</v>
@@ -11682,10 +11682,10 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>45.29182899914638</v>
+        <v>45.2918289559292</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>7.502095955281508</v>
+        <v>7.502096023726494</v>
       </c>
       <c r="J212" s="2" t="n">
         <v>0.5033337665933346</v>
@@ -11700,7 +11700,7 @@
         <v>-1</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>0.1731823518650477</v>
+        <v>0.173182351624705</v>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v/>
       </c>
       <c r="D213" s="2" t="n">
-        <v>174.5956628356439</v>
+        <v>174.5956628356512</v>
       </c>
       <c r="E213" s="2" t="n">
         <v>11.45</v>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>35.49117076994925</v>
+        <v>35.49117092109205</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>12.06152083125118</v>
+        <v>12.06152092848858</v>
       </c>
       <c r="J213" s="2" t="n">
         <v>1.37491209646732</v>
@@ -11753,7 +11753,7 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>-0.0379791186690562</v>
+        <v>-0.0379791187051067</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v/>
       </c>
       <c r="D214" s="2" t="n">
-        <v>167.9528976821928</v>
+        <v>167.9528976821931</v>
       </c>
       <c r="E214" s="2" t="n">
         <v>110.5</v>
@@ -11788,10 +11788,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>51.59130265354641</v>
+        <v>51.59130271020619</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>19.47860951936617</v>
+        <v>19.47860946345231</v>
       </c>
       <c r="J214" s="2" t="n">
         <v>0.5884993518823972</v>
@@ -11806,7 +11806,7 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>1.327409057392304</v>
+        <v>1.327409057500454</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
@@ -11841,10 +11841,10 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>44.74057439358984</v>
+        <v>44.74057404021639</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>12.39852815184873</v>
+        <v>12.39852840515644</v>
       </c>
       <c r="J215" s="2" t="n">
         <v>0.3691331351798802</v>
@@ -11859,7 +11859,7 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>-0.0217667191559064</v>
+        <v>-0.021766719071787</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v/>
       </c>
       <c r="D216" s="2" t="n">
-        <v>155.0800571577178</v>
+        <v>155.0800571577176</v>
       </c>
       <c r="E216" s="2" t="n">
         <v>60.7</v>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>37.40266254749204</v>
+        <v>37.40266187459815</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>16.9552013375014</v>
+        <v>16.95520146486602</v>
       </c>
       <c r="J216" s="2" t="n">
         <v>0.6223271994782915</v>
@@ -11912,7 +11912,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>0.1789441313758286</v>
+        <v>0.1789441319526616</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v/>
       </c>
       <c r="D217" s="2" t="n">
-        <v>149.5476668099933</v>
+        <v>149.5476668099932</v>
       </c>
       <c r="E217" s="2" t="n">
         <v>14.5</v>
@@ -11950,7 +11950,7 @@
         <v>50.18885051636709</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>14.8838030943297</v>
+        <v>14.88380315288808</v>
       </c>
       <c r="J217" s="2" t="n">
         <v>0.4040662618474863</v>
@@ -11965,7 +11965,7 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>0.1286082002245973</v>
+        <v>0.1286082001885431</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -12000,10 +12000,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>50.61079856207949</v>
+        <v>50.61079854708571</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>16.95550470689485</v>
+        <v>16.95550475690656</v>
       </c>
       <c r="J218" s="2" t="n">
         <v>0.7032753193057611</v>
@@ -12018,7 +12018,7 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>0.0698231583319463</v>
+        <v>0.0698231584280864</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v/>
       </c>
       <c r="D219" s="2" t="n">
-        <v>143.8008819893764</v>
+        <v>143.8008819893754</v>
       </c>
       <c r="E219" s="2" t="n">
         <v>42.1</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>51.02256767578415</v>
+        <v>51.02256768660532</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>9.398868562918905</v>
+        <v>9.39886858204467</v>
       </c>
       <c r="J219" s="2" t="n">
         <v>0.3806519612675255</v>
@@ -12071,7 +12071,7 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>0.3018795647520191</v>
+        <v>0.3018795646198253</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
@@ -12106,10 +12106,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>48.13639197231801</v>
+        <v>48.13639225278521</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>12.92685616619942</v>
+        <v>12.92685621161646</v>
       </c>
       <c r="J220" s="2" t="n">
         <v>0.2131699292150263</v>
@@ -12124,7 +12124,7 @@
         <v>-1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>-0.0906360841044387</v>
+        <v>-0.09063608430873379</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v/>
       </c>
       <c r="D221" s="2" t="n">
-        <v>116.275147788426</v>
+        <v>116.2751477884266</v>
       </c>
       <c r="E221" s="2" t="n">
         <v>49</v>
@@ -12159,10 +12159,10 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>40.5614693460153</v>
+        <v>40.56146930639611</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>15.32268281298088</v>
+        <v>15.32268279477568</v>
       </c>
       <c r="J221" s="2" t="n">
         <v>1.035506494536956</v>
@@ -12177,7 +12177,7 @@
         <v>-1</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>-0.2257849322334141</v>
+        <v>-0.2257849323535882</v>
       </c>
       <c r="O221" s="2" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v/>
       </c>
       <c r="D222" s="2" t="n">
-        <v>94.85169220505654</v>
+        <v>94.85169220505652</v>
       </c>
       <c r="E222" s="2" t="n">
         <v>37.95</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>41.98483309885246</v>
+        <v>41.98483327885389</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>18.5866883904592</v>
+        <v>18.58668843931327</v>
       </c>
       <c r="J222" s="2" t="n">
         <v>0.6672973893879089</v>
@@ -12230,7 +12230,7 @@
         <v>-1</v>
       </c>
       <c r="N222" s="2" t="n">
-        <v>0.0325814839545374</v>
+        <v>0.0325814836420826</v>
       </c>
       <c r="O222" s="2" t="inlineStr">
         <is>
